--- a/research/traditional_assets/database/data/qatar/qatar_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_construction_supplies.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08149645888973223</v>
+        <v>0.08145546243084248</v>
       </c>
       <c r="C2">
-        <v>817.2809569796249</v>
+        <v>809.7349917931153</v>
       </c>
       <c r="D2">
-        <v>655.1809569796249</v>
+        <v>655.7309917931153</v>
       </c>
       <c r="E2">
-        <v>-284.4</v>
+        <v>-276.304</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.096</v>
       </c>
       <c r="G2">
         <v>162.1</v>
@@ -1579,28 +1579,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4072288</v>
       </c>
       <c r="N2">
-        <v>53.12222222222221</v>
+        <v>52.71499342222221</v>
       </c>
       <c r="O2">
-        <v>5.312222222222221</v>
+        <v>5.271499342222222</v>
       </c>
       <c r="P2">
-        <v>47.80999999999999</v>
+        <v>47.44349407999999</v>
       </c>
       <c r="Q2">
-        <v>66.91</v>
+        <v>66.54349407999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08149645888973223</v>
+        <v>0.08182097215236614</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7219921178713897</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>130.4480975368692</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08145546243084248</v>
+        <v>0.08141446597195276</v>
       </c>
       <c r="C3">
-        <v>809.7349917931153</v>
+        <v>802.1899509084855</v>
       </c>
       <c r="D3">
-        <v>655.7309917931153</v>
+        <v>656.2819509084854</v>
       </c>
       <c r="E3">
-        <v>-276.304</v>
+        <v>-268.208</v>
       </c>
       <c r="F3">
-        <v>8.096</v>
+        <v>16.192</v>
       </c>
       <c r="G3">
         <v>162.1</v>
@@ -1661,28 +1661,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M3">
-        <v>0.4072288</v>
+        <v>0.8144576</v>
       </c>
       <c r="N3">
-        <v>52.71499342222221</v>
+        <v>52.30776462222222</v>
       </c>
       <c r="O3">
-        <v>5.271499342222222</v>
+        <v>5.230776462222222</v>
       </c>
       <c r="P3">
-        <v>47.44349407999999</v>
+        <v>47.07698815999999</v>
       </c>
       <c r="Q3">
-        <v>66.54349407999999</v>
+        <v>66.17698815999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08182097215236614</v>
+        <v>0.08215210813464567</v>
       </c>
       <c r="T3">
-        <v>0.7219921178713897</v>
+        <v>0.7286292949064274</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>130.4480975368692</v>
+        <v>65.22404876843461</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08141446597195276</v>
+        <v>0.08137346951306301</v>
       </c>
       <c r="C4">
-        <v>802.1899509084855</v>
+        <v>794.6458366575496</v>
       </c>
       <c r="D4">
-        <v>656.2819509084854</v>
+        <v>656.8338366575496</v>
       </c>
       <c r="E4">
-        <v>-268.208</v>
+        <v>-260.112</v>
       </c>
       <c r="F4">
-        <v>16.192</v>
+        <v>24.288</v>
       </c>
       <c r="G4">
         <v>162.1</v>
@@ -1743,28 +1743,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M4">
-        <v>0.8144576</v>
+        <v>1.2216864</v>
       </c>
       <c r="N4">
-        <v>52.30776462222222</v>
+        <v>51.90053582222221</v>
       </c>
       <c r="O4">
-        <v>5.230776462222222</v>
+        <v>5.190053582222221</v>
       </c>
       <c r="P4">
-        <v>47.07698815999999</v>
+        <v>46.71048223999999</v>
       </c>
       <c r="Q4">
-        <v>66.17698815999999</v>
+        <v>65.81048224</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08215210813464567</v>
+        <v>0.08249007166295157</v>
       </c>
       <c r="T4">
-        <v>0.7286292949064274</v>
+        <v>0.7354033209524966</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.22404876843461</v>
+        <v>43.48269917895641</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08137346951306301</v>
+        <v>0.08133247305417329</v>
       </c>
       <c r="C5">
-        <v>794.6458366575496</v>
+        <v>787.1026513799704</v>
       </c>
       <c r="D5">
-        <v>656.8338366575496</v>
+        <v>657.3866513799704</v>
       </c>
       <c r="E5">
-        <v>-260.112</v>
+        <v>-252.016</v>
       </c>
       <c r="F5">
-        <v>24.288</v>
+        <v>32.384</v>
       </c>
       <c r="G5">
         <v>162.1</v>
@@ -1825,28 +1825,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M5">
-        <v>1.2216864</v>
+        <v>1.6289152</v>
       </c>
       <c r="N5">
-        <v>51.90053582222221</v>
+        <v>51.49330702222221</v>
       </c>
       <c r="O5">
-        <v>5.190053582222221</v>
+        <v>5.149330702222222</v>
       </c>
       <c r="P5">
-        <v>46.71048223999999</v>
+        <v>46.34397631999999</v>
       </c>
       <c r="Q5">
-        <v>65.81048224</v>
+        <v>65.44397631999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08249007166295157</v>
+        <v>0.08283507609809718</v>
       </c>
       <c r="T5">
-        <v>0.7354033209524966</v>
+        <v>0.7423184725411924</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.48269917895641</v>
+        <v>32.61202438421731</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08133247305417329</v>
+        <v>0.08129147659528356</v>
       </c>
       <c r="C6">
-        <v>787.1026513799704</v>
+        <v>779.5603974232955</v>
       </c>
       <c r="D6">
-        <v>657.3866513799704</v>
+        <v>657.9403974232955</v>
       </c>
       <c r="E6">
-        <v>-252.016</v>
+        <v>-243.92</v>
       </c>
       <c r="F6">
-        <v>32.384</v>
+        <v>40.48</v>
       </c>
       <c r="G6">
         <v>162.1</v>
@@ -1907,28 +1907,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M6">
-        <v>1.6289152</v>
+        <v>2.036144</v>
       </c>
       <c r="N6">
-        <v>51.49330702222221</v>
+        <v>51.08607822222221</v>
       </c>
       <c r="O6">
-        <v>5.149330702222222</v>
+        <v>5.108607822222222</v>
       </c>
       <c r="P6">
-        <v>46.34397631999999</v>
+        <v>45.97747039999999</v>
       </c>
       <c r="Q6">
-        <v>65.44397631999999</v>
+        <v>65.07747039999998</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08283507609809718</v>
+        <v>0.08318734378450901</v>
       </c>
       <c r="T6">
-        <v>0.7423184725411924</v>
+        <v>0.7493792062685974</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.61202438421731</v>
+        <v>26.08961950737384</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08129147659528356</v>
+        <v>0.08125048013639383</v>
       </c>
       <c r="C7">
-        <v>779.5603974232955</v>
+        <v>772.0190771429878</v>
       </c>
       <c r="D7">
-        <v>657.9403974232955</v>
+        <v>658.4950771429878</v>
       </c>
       <c r="E7">
-        <v>-243.92</v>
+        <v>-235.824</v>
       </c>
       <c r="F7">
-        <v>40.48</v>
+        <v>48.57600000000001</v>
       </c>
       <c r="G7">
         <v>162.1</v>
@@ -1989,28 +1989,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M7">
-        <v>2.036144</v>
+        <v>2.4433728</v>
       </c>
       <c r="N7">
-        <v>51.08607822222221</v>
+        <v>50.67884942222221</v>
       </c>
       <c r="O7">
-        <v>5.108607822222222</v>
+        <v>5.067884942222221</v>
       </c>
       <c r="P7">
-        <v>45.97747039999999</v>
+        <v>45.61096447999999</v>
       </c>
       <c r="Q7">
-        <v>65.07747039999998</v>
+        <v>64.71096448</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08318734378450901</v>
+        <v>0.08354710652807854</v>
       </c>
       <c r="T7">
-        <v>0.7493792062685974</v>
+        <v>0.7565901683731815</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.08961950737384</v>
+        <v>21.7413495894782</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08125048013639383</v>
+        <v>0.08120948367750409</v>
       </c>
       <c r="C8">
-        <v>772.0190771429878</v>
+        <v>764.4786929024609</v>
       </c>
       <c r="D8">
-        <v>658.4950771429878</v>
+        <v>659.0506929024609</v>
       </c>
       <c r="E8">
-        <v>-235.824</v>
+        <v>-227.728</v>
       </c>
       <c r="F8">
-        <v>48.576</v>
+        <v>56.672</v>
       </c>
       <c r="G8">
         <v>162.1</v>
@@ -2071,28 +2071,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M8">
-        <v>2.4433728</v>
+        <v>2.8506016</v>
       </c>
       <c r="N8">
-        <v>50.67884942222221</v>
+        <v>50.27162062222222</v>
       </c>
       <c r="O8">
-        <v>5.067884942222221</v>
+        <v>5.027162062222222</v>
       </c>
       <c r="P8">
-        <v>45.61096447999999</v>
+        <v>45.24445855999999</v>
       </c>
       <c r="Q8">
-        <v>64.71096448</v>
+        <v>64.34445855999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08354710652807854</v>
+        <v>0.08391460610484311</v>
       </c>
       <c r="T8">
-        <v>0.7565901683731815</v>
+        <v>0.7639562049316274</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.7413495894782</v>
+        <v>18.63544250526704</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08120948367750409</v>
+        <v>0.08116848721861436</v>
       </c>
       <c r="C9">
-        <v>764.4786929024609</v>
+        <v>756.9392470731108</v>
       </c>
       <c r="D9">
-        <v>659.0506929024609</v>
+        <v>659.6072470731108</v>
       </c>
       <c r="E9">
-        <v>-227.728</v>
+        <v>-219.632</v>
       </c>
       <c r="F9">
-        <v>56.672</v>
+        <v>64.768</v>
       </c>
       <c r="G9">
         <v>162.1</v>
@@ -2153,28 +2153,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M9">
-        <v>2.8506016</v>
+        <v>3.2578304</v>
       </c>
       <c r="N9">
-        <v>50.27162062222222</v>
+        <v>49.86439182222221</v>
       </c>
       <c r="O9">
-        <v>5.027162062222222</v>
+        <v>4.986439182222221</v>
       </c>
       <c r="P9">
-        <v>45.24445855999999</v>
+        <v>44.87795263999999</v>
       </c>
       <c r="Q9">
-        <v>64.34445855999999</v>
+        <v>63.97795263999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08391460610484311</v>
+        <v>0.08429009480284169</v>
       </c>
       <c r="T9">
-        <v>0.7639562049316275</v>
+        <v>0.7714823727196048</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.63544250526703</v>
+        <v>16.30601219210865</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08116848721861436</v>
+        <v>0.08112749075972464</v>
       </c>
       <c r="C10">
-        <v>756.9392470731108</v>
+        <v>749.4007420343511</v>
       </c>
       <c r="D10">
-        <v>659.6072470731108</v>
+        <v>660.1647420343511</v>
       </c>
       <c r="E10">
-        <v>-219.632</v>
+        <v>-211.536</v>
       </c>
       <c r="F10">
-        <v>64.768</v>
+        <v>72.864</v>
       </c>
       <c r="G10">
         <v>162.1</v>
@@ -2235,28 +2235,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M10">
-        <v>3.2578304</v>
+        <v>3.6650592</v>
       </c>
       <c r="N10">
-        <v>49.86439182222221</v>
+        <v>49.45716302222221</v>
       </c>
       <c r="O10">
-        <v>4.986439182222221</v>
+        <v>4.945716302222221</v>
       </c>
       <c r="P10">
-        <v>44.87795263999999</v>
+        <v>44.51144671999999</v>
       </c>
       <c r="Q10">
-        <v>63.97795263999999</v>
+        <v>63.61144671999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08429009480284169</v>
+        <v>0.0846738359996974</v>
       </c>
       <c r="T10">
-        <v>0.7714823727196048</v>
+        <v>0.7791739507886367</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.30601219210865</v>
+        <v>14.49423305965214</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08112749075972464</v>
+        <v>0.08108649430083489</v>
       </c>
       <c r="C11">
-        <v>749.4007420343511</v>
+        <v>741.8631801736473</v>
       </c>
       <c r="D11">
-        <v>660.1647420343511</v>
+        <v>660.7231801736473</v>
       </c>
       <c r="E11">
-        <v>-211.536</v>
+        <v>-203.44</v>
       </c>
       <c r="F11">
-        <v>72.864</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="G11">
         <v>162.1</v>
@@ -2317,28 +2317,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M11">
-        <v>3.6650592</v>
+        <v>4.072287999999999</v>
       </c>
       <c r="N11">
-        <v>49.45716302222221</v>
+        <v>49.04993422222221</v>
       </c>
       <c r="O11">
-        <v>4.945716302222221</v>
+        <v>4.904993422222222</v>
       </c>
       <c r="P11">
-        <v>44.51144671999999</v>
+        <v>44.14494079999999</v>
       </c>
       <c r="Q11">
-        <v>63.61144671999999</v>
+        <v>63.24494079999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0846738359996974</v>
+        <v>0.08506610477870544</v>
       </c>
       <c r="T11">
-        <v>0.7791739507886367</v>
+        <v>0.7870364528147582</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.49423305965214</v>
+        <v>13.04480975368693</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08108649430083489</v>
+        <v>0.08119399784194517</v>
       </c>
       <c r="C12">
-        <v>741.8631801736473</v>
+        <v>732.3048129944367</v>
       </c>
       <c r="D12">
-        <v>660.7231801736473</v>
+        <v>659.2608129944367</v>
       </c>
       <c r="E12">
-        <v>-203.44</v>
+        <v>-195.344</v>
       </c>
       <c r="F12">
-        <v>80.96000000000001</v>
+        <v>89.056</v>
       </c>
       <c r="G12">
         <v>162.1</v>
@@ -2399,45 +2399,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M12">
-        <v>4.072288</v>
+        <v>4.6131008</v>
       </c>
       <c r="N12">
-        <v>49.04993422222221</v>
+        <v>48.50912142222221</v>
       </c>
       <c r="O12">
-        <v>4.904993422222222</v>
+        <v>4.850912142222222</v>
       </c>
       <c r="P12">
-        <v>44.14494079999999</v>
+        <v>43.65820927999999</v>
       </c>
       <c r="Q12">
-        <v>63.24494079999999</v>
+        <v>62.75820928</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08506610477870544</v>
+        <v>0.08546718858645524</v>
       </c>
       <c r="T12">
-        <v>0.7870364528147582</v>
+        <v>0.7950756402796688</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.04480975368692</v>
+        <v>11.51551299772644</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08119399784194517</v>
+        <v>0.08116650138305544</v>
       </c>
       <c r="C13">
-        <v>732.3048129944367</v>
+        <v>724.5822299804537</v>
       </c>
       <c r="D13">
-        <v>659.2608129944367</v>
+        <v>659.6342299804537</v>
       </c>
       <c r="E13">
-        <v>-195.344</v>
+        <v>-187.248</v>
       </c>
       <c r="F13">
-        <v>89.056</v>
+        <v>97.152</v>
       </c>
       <c r="G13">
         <v>162.1</v>
@@ -2481,28 +2481,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M13">
-        <v>4.6131008</v>
+        <v>5.0324736</v>
       </c>
       <c r="N13">
-        <v>48.50912142222221</v>
+        <v>48.08974862222221</v>
       </c>
       <c r="O13">
-        <v>4.850912142222222</v>
+        <v>4.808974862222222</v>
       </c>
       <c r="P13">
-        <v>43.65820927999999</v>
+        <v>43.28077375999999</v>
       </c>
       <c r="Q13">
-        <v>62.75820928</v>
+        <v>62.38077375999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08546718858645524</v>
+        <v>0.08587738793529026</v>
       </c>
       <c r="T13">
-        <v>0.7950756402796688</v>
+        <v>0.8032975365506003</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.51551299772644</v>
+        <v>10.55588691458256</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08116650138305544</v>
+        <v>0.0813379049241657</v>
       </c>
       <c r="C14">
-        <v>724.5822299804537</v>
+        <v>714.1653521252846</v>
       </c>
       <c r="D14">
-        <v>659.6342299804537</v>
+        <v>657.3133521252846</v>
       </c>
       <c r="E14">
-        <v>-187.248</v>
+        <v>-179.152</v>
       </c>
       <c r="F14">
-        <v>97.152</v>
+        <v>105.248</v>
       </c>
       <c r="G14">
         <v>162.1</v>
@@ -2563,45 +2563,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M14">
-        <v>5.0324736</v>
+        <v>5.630768</v>
       </c>
       <c r="N14">
-        <v>48.08974862222221</v>
+        <v>47.49145422222222</v>
       </c>
       <c r="O14">
-        <v>4.808974862222222</v>
+        <v>4.749145422222222</v>
       </c>
       <c r="P14">
-        <v>43.28077375999999</v>
+        <v>42.7423088</v>
       </c>
       <c r="Q14">
-        <v>62.38077375999999</v>
+        <v>61.8423088</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08587738793529026</v>
+        <v>0.08629701715421345</v>
       </c>
       <c r="T14">
-        <v>0.8032975365506003</v>
+        <v>0.8117084419312083</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.55588691458256</v>
+        <v>9.434276500509739</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0813379049241657</v>
+        <v>0.08132570846527597</v>
       </c>
       <c r="C15">
-        <v>714.1653521252846</v>
+        <v>706.2339575956946</v>
       </c>
       <c r="D15">
-        <v>657.3133521252846</v>
+        <v>657.4779575956946</v>
       </c>
       <c r="E15">
-        <v>-179.152</v>
+        <v>-171.056</v>
       </c>
       <c r="F15">
-        <v>105.248</v>
+        <v>113.344</v>
       </c>
       <c r="G15">
         <v>162.1</v>
@@ -2645,28 +2645,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M15">
-        <v>5.630768</v>
+        <v>6.063904</v>
       </c>
       <c r="N15">
-        <v>47.49145422222222</v>
+        <v>47.05831822222221</v>
       </c>
       <c r="O15">
-        <v>4.749145422222222</v>
+        <v>4.705831822222222</v>
       </c>
       <c r="P15">
-        <v>42.7423088</v>
+        <v>42.35248639999999</v>
       </c>
       <c r="Q15">
-        <v>61.8423088</v>
+        <v>61.45248639999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08629701715421345</v>
+        <v>0.08672640519218136</v>
       </c>
       <c r="T15">
-        <v>0.8117084419312083</v>
+        <v>0.8203149497625281</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.434276500509739</v>
+        <v>8.760399607616185</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08132570846527597</v>
+        <v>0.08131351200638626</v>
       </c>
       <c r="C16">
-        <v>706.2339575956946</v>
+        <v>698.3026455282899</v>
       </c>
       <c r="D16">
-        <v>657.4779575956946</v>
+        <v>657.6426455282899</v>
       </c>
       <c r="E16">
-        <v>-171.056</v>
+        <v>-162.96</v>
       </c>
       <c r="F16">
-        <v>113.344</v>
+        <v>121.44</v>
       </c>
       <c r="G16">
         <v>162.1</v>
@@ -2727,28 +2727,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M16">
-        <v>6.063904</v>
+        <v>6.497040000000001</v>
       </c>
       <c r="N16">
-        <v>47.05831822222221</v>
+        <v>46.62518222222221</v>
       </c>
       <c r="O16">
-        <v>4.705831822222222</v>
+        <v>4.662518222222221</v>
       </c>
       <c r="P16">
-        <v>42.35248639999999</v>
+        <v>41.96266399999999</v>
       </c>
       <c r="Q16">
-        <v>61.45248639999999</v>
+        <v>61.06266399999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08672640519218136</v>
+        <v>0.08716589647810147</v>
       </c>
       <c r="T16">
-        <v>0.8203149497625281</v>
+        <v>0.8291239636604673</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.760399607616185</v>
+        <v>8.176372967108438</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08131351200638626</v>
+        <v>0.08130131554749651</v>
       </c>
       <c r="C17">
-        <v>698.30264552829</v>
+        <v>690.3714159850531</v>
       </c>
       <c r="D17">
-        <v>657.6426455282899</v>
+        <v>657.807415985053</v>
       </c>
       <c r="E17">
-        <v>-162.96</v>
+        <v>-154.864</v>
       </c>
       <c r="F17">
-        <v>121.44</v>
+        <v>129.536</v>
       </c>
       <c r="G17">
         <v>162.1</v>
@@ -2809,28 +2809,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M17">
-        <v>6.49704</v>
+        <v>6.930176</v>
       </c>
       <c r="N17">
-        <v>46.62518222222221</v>
+        <v>46.19204622222221</v>
       </c>
       <c r="O17">
-        <v>4.662518222222221</v>
+        <v>4.619204622222221</v>
       </c>
       <c r="P17">
-        <v>41.96266399999999</v>
+        <v>41.57284159999999</v>
       </c>
       <c r="Q17">
-        <v>61.06266399999999</v>
+        <v>60.67284159999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08716589647810147</v>
+        <v>0.08761585184225774</v>
       </c>
       <c r="T17">
-        <v>0.8291239636604673</v>
+        <v>0.8381427159845477</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.176372967108438</v>
+        <v>7.665349656664161</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08130131554749651</v>
+        <v>0.08141151908860678</v>
       </c>
       <c r="C18">
-        <v>690.3714159850531</v>
+        <v>680.7895902975304</v>
       </c>
       <c r="D18">
-        <v>657.807415985053</v>
+        <v>656.3215902975303</v>
       </c>
       <c r="E18">
-        <v>-154.864</v>
+        <v>-146.768</v>
       </c>
       <c r="F18">
-        <v>129.536</v>
+        <v>137.632</v>
       </c>
       <c r="G18">
         <v>162.1</v>
@@ -2891,45 +2891,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M18">
-        <v>6.930176</v>
+        <v>7.4734176</v>
       </c>
       <c r="N18">
-        <v>46.19204622222221</v>
+        <v>45.64880462222222</v>
       </c>
       <c r="O18">
-        <v>4.619204622222221</v>
+        <v>4.564880462222222</v>
       </c>
       <c r="P18">
-        <v>41.57284159999999</v>
+        <v>41.08392416</v>
       </c>
       <c r="Q18">
-        <v>60.67284159999999</v>
+        <v>60.18392416</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08761585184225774</v>
+        <v>0.08807664950434552</v>
       </c>
       <c r="T18">
-        <v>0.8381427159845477</v>
+        <v>0.8473787876417386</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.665349656664161</v>
+        <v>7.10815654436629</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08141151908860678</v>
+        <v>0.08140652262971704</v>
       </c>
       <c r="C19">
-        <v>680.7895902975304</v>
+        <v>672.7608100694376</v>
       </c>
       <c r="D19">
-        <v>656.3215902975303</v>
+        <v>656.3888100694377</v>
       </c>
       <c r="E19">
-        <v>-146.768</v>
+        <v>-138.672</v>
       </c>
       <c r="F19">
-        <v>137.632</v>
+        <v>145.728</v>
       </c>
       <c r="G19">
         <v>162.1</v>
@@ -2973,28 +2973,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M19">
-        <v>7.4734176</v>
+        <v>7.9130304</v>
       </c>
       <c r="N19">
-        <v>45.64880462222222</v>
+        <v>45.20919182222221</v>
       </c>
       <c r="O19">
-        <v>4.564880462222222</v>
+        <v>4.520919182222221</v>
       </c>
       <c r="P19">
-        <v>41.08392416</v>
+        <v>40.68827263999999</v>
       </c>
       <c r="Q19">
-        <v>60.18392416</v>
+        <v>59.78827263999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08807664950434552</v>
+        <v>0.08854868613380126</v>
       </c>
       <c r="T19">
-        <v>0.8473787876417386</v>
+        <v>0.8568401293393487</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.10815654436629</v>
+        <v>6.713258958568162</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08140652262971704</v>
+        <v>0.08140152617082731</v>
       </c>
       <c r="C20">
-        <v>672.7608100694376</v>
+        <v>664.732043611913</v>
       </c>
       <c r="D20">
-        <v>656.3888100694377</v>
+        <v>656.4560436119131</v>
       </c>
       <c r="E20">
-        <v>-138.672</v>
+        <v>-130.576</v>
       </c>
       <c r="F20">
-        <v>145.728</v>
+        <v>153.824</v>
       </c>
       <c r="G20">
         <v>162.1</v>
@@ -3055,28 +3055,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M20">
-        <v>7.9130304</v>
+        <v>8.352643200000001</v>
       </c>
       <c r="N20">
-        <v>45.20919182222221</v>
+        <v>44.76957902222221</v>
       </c>
       <c r="O20">
-        <v>4.520919182222221</v>
+        <v>4.476957902222221</v>
       </c>
       <c r="P20">
-        <v>40.68827263999999</v>
+        <v>40.29262111999999</v>
       </c>
       <c r="Q20">
-        <v>59.78827263999999</v>
+        <v>59.39262111999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08854868613380126</v>
+        <v>0.08903237798867569</v>
       </c>
       <c r="T20">
-        <v>0.8568401293393487</v>
+        <v>0.8665350844122085</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.713258958568162</v>
+        <v>6.359929539696153</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08140152617082731</v>
+        <v>0.08157652971193759</v>
       </c>
       <c r="C21">
-        <v>664.732043611913</v>
+        <v>654.2893321796128</v>
       </c>
       <c r="D21">
-        <v>656.4560436119131</v>
+        <v>654.1093321796128</v>
       </c>
       <c r="E21">
-        <v>-130.576</v>
+        <v>-122.48</v>
       </c>
       <c r="F21">
-        <v>153.824</v>
+        <v>161.92</v>
       </c>
       <c r="G21">
         <v>162.1</v>
@@ -3137,45 +3137,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M21">
-        <v>8.352643200000001</v>
+        <v>8.954176</v>
       </c>
       <c r="N21">
-        <v>44.76957902222221</v>
+        <v>44.16804622222222</v>
       </c>
       <c r="O21">
-        <v>4.476957902222221</v>
+        <v>4.416804622222222</v>
       </c>
       <c r="P21">
-        <v>40.29262111999999</v>
+        <v>39.75124159999999</v>
       </c>
       <c r="Q21">
-        <v>59.39262111999999</v>
+        <v>58.85124159999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08903237798867569</v>
+        <v>0.08952816213992197</v>
       </c>
       <c r="T21">
-        <v>0.8665350844122085</v>
+        <v>0.8764724133618899</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.359929539696153</v>
+        <v>5.932675683638808</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08157652971193759</v>
+        <v>0.08158053325304784</v>
       </c>
       <c r="C22">
-        <v>654.2893321796128</v>
+        <v>646.139842952367</v>
       </c>
       <c r="D22">
-        <v>654.1093321796128</v>
+        <v>654.055842952367</v>
       </c>
       <c r="E22">
-        <v>-122.48</v>
+        <v>-114.384</v>
       </c>
       <c r="F22">
-        <v>161.92</v>
+        <v>170.016</v>
       </c>
       <c r="G22">
         <v>162.1</v>
@@ -3219,28 +3219,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M22">
-        <v>8.954176</v>
+        <v>9.401884800000001</v>
       </c>
       <c r="N22">
-        <v>44.16804622222222</v>
+        <v>43.72033742222222</v>
       </c>
       <c r="O22">
-        <v>4.416804622222222</v>
+        <v>4.372033742222222</v>
       </c>
       <c r="P22">
-        <v>39.75124159999999</v>
+        <v>39.34830367999999</v>
       </c>
       <c r="Q22">
-        <v>58.85124159999999</v>
+        <v>58.44830368</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08952816213992197</v>
+        <v>0.09003649778866815</v>
       </c>
       <c r="T22">
-        <v>0.8764724133618899</v>
+        <v>0.8866613202596643</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.932675683638808</v>
+        <v>5.650167317751246</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08158053325304784</v>
+        <v>0.08158453679415811</v>
       </c>
       <c r="C23">
-        <v>646.1398429523671</v>
+        <v>637.9903624724769</v>
       </c>
       <c r="D23">
-        <v>654.055842952367</v>
+        <v>654.0023624724769</v>
       </c>
       <c r="E23">
-        <v>-114.384</v>
+        <v>-106.288</v>
       </c>
       <c r="F23">
-        <v>170.016</v>
+        <v>178.112</v>
       </c>
       <c r="G23">
         <v>162.1</v>
@@ -3301,28 +3301,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M23">
-        <v>9.401884799999999</v>
+        <v>9.8495936</v>
       </c>
       <c r="N23">
-        <v>43.72033742222222</v>
+        <v>43.27262862222221</v>
       </c>
       <c r="O23">
-        <v>4.372033742222222</v>
+        <v>4.327262862222222</v>
       </c>
       <c r="P23">
-        <v>39.34830367999999</v>
+        <v>38.94536575999999</v>
       </c>
       <c r="Q23">
-        <v>58.44830368</v>
+        <v>58.04536576</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09003649778866815</v>
+        <v>0.09055786768481809</v>
       </c>
       <c r="T23">
-        <v>0.8866613202596643</v>
+        <v>0.8971114811804586</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.650167317751247</v>
+        <v>5.393341530580735</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08158453679415811</v>
+        <v>0.08158854033526838</v>
       </c>
       <c r="C24">
-        <v>637.9903624724769</v>
+        <v>629.8408907377966</v>
       </c>
       <c r="D24">
-        <v>654.0023624724769</v>
+        <v>653.9488907377967</v>
       </c>
       <c r="E24">
-        <v>-106.288</v>
+        <v>-98.19199999999995</v>
       </c>
       <c r="F24">
-        <v>178.112</v>
+        <v>186.208</v>
       </c>
       <c r="G24">
         <v>162.1</v>
@@ -3383,28 +3383,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M24">
-        <v>9.8495936</v>
+        <v>10.2973024</v>
       </c>
       <c r="N24">
-        <v>43.27262862222221</v>
+        <v>42.82491982222221</v>
       </c>
       <c r="O24">
-        <v>4.327262862222222</v>
+        <v>4.282491982222221</v>
       </c>
       <c r="P24">
-        <v>38.94536575999999</v>
+        <v>38.54242783999999</v>
       </c>
       <c r="Q24">
-        <v>58.04536576</v>
+        <v>57.64242784</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09055786768481809</v>
+        <v>0.0910927796561927</v>
       </c>
       <c r="T24">
-        <v>0.8971114811804586</v>
+        <v>0.9078330748524425</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.393341530580735</v>
+        <v>5.158848420555485</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08158854033526838</v>
+        <v>0.08159254387637865</v>
       </c>
       <c r="C25">
-        <v>629.8408907377966</v>
+        <v>621.6914277461819</v>
       </c>
       <c r="D25">
-        <v>653.9488907377967</v>
+        <v>653.8954277461819</v>
       </c>
       <c r="E25">
-        <v>-98.19199999999995</v>
+        <v>-90.09599999999995</v>
       </c>
       <c r="F25">
-        <v>186.208</v>
+        <v>194.304</v>
       </c>
       <c r="G25">
         <v>162.1</v>
@@ -3465,28 +3465,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M25">
-        <v>10.2973024</v>
+        <v>10.7450112</v>
       </c>
       <c r="N25">
-        <v>42.82491982222221</v>
+        <v>42.37721102222221</v>
       </c>
       <c r="O25">
-        <v>4.282491982222221</v>
+        <v>4.237721102222221</v>
       </c>
       <c r="P25">
-        <v>38.54242783999999</v>
+        <v>38.13948991999999</v>
       </c>
       <c r="Q25">
-        <v>57.64242784</v>
+        <v>57.23948991999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0910927796561927</v>
+        <v>0.09164176825839296</v>
       </c>
       <c r="T25">
-        <v>0.9078330748524425</v>
+        <v>0.9188368157263206</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.158848420555485</v>
+        <v>4.94389640303234</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08159254387637865</v>
+        <v>0.08159654741748891</v>
       </c>
       <c r="C26">
-        <v>621.6914277461819</v>
+        <v>613.5419734954883</v>
       </c>
       <c r="D26">
-        <v>653.8954277461819</v>
+        <v>653.8419734954882</v>
       </c>
       <c r="E26">
-        <v>-90.09599999999998</v>
+        <v>-81.99999999999997</v>
       </c>
       <c r="F26">
-        <v>194.304</v>
+        <v>202.4</v>
       </c>
       <c r="G26">
         <v>162.1</v>
@@ -3547,28 +3547,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M26">
-        <v>10.7450112</v>
+        <v>11.19272</v>
       </c>
       <c r="N26">
-        <v>42.37721102222221</v>
+        <v>41.92950222222221</v>
       </c>
       <c r="O26">
-        <v>4.237721102222221</v>
+        <v>4.192950222222222</v>
       </c>
       <c r="P26">
-        <v>38.13948991999999</v>
+        <v>37.73655199999999</v>
       </c>
       <c r="Q26">
-        <v>57.23948991999999</v>
+        <v>56.83655199999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09164176825839296</v>
+        <v>0.09220539655665189</v>
       </c>
       <c r="T26">
-        <v>0.9188368157263206</v>
+        <v>0.9301339896901688</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.94389640303234</v>
+        <v>4.746140546911047</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08159654741748891</v>
+        <v>0.08160055095859918</v>
       </c>
       <c r="C27">
-        <v>613.5419734954883</v>
+        <v>605.392527983572</v>
       </c>
       <c r="D27">
-        <v>653.8419734954882</v>
+        <v>653.788527983572</v>
       </c>
       <c r="E27">
-        <v>-81.99999999999997</v>
+        <v>-73.90399999999997</v>
       </c>
       <c r="F27">
-        <v>202.4</v>
+        <v>210.496</v>
       </c>
       <c r="G27">
         <v>162.1</v>
@@ -3629,28 +3629,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M27">
-        <v>11.19272</v>
+        <v>11.6404288</v>
       </c>
       <c r="N27">
-        <v>41.92950222222221</v>
+        <v>41.48179342222221</v>
       </c>
       <c r="O27">
-        <v>4.192950222222222</v>
+        <v>4.148179342222221</v>
       </c>
       <c r="P27">
-        <v>37.73655199999999</v>
+        <v>37.33361407999999</v>
       </c>
       <c r="Q27">
-        <v>56.83655199999999</v>
+        <v>56.43361407999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09220539655665189</v>
+        <v>0.09278425805216106</v>
       </c>
       <c r="T27">
-        <v>0.9301339896901688</v>
+        <v>0.941736492680067</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.746140546911047</v>
+        <v>4.56359667972216</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08160055095859918</v>
+        <v>0.08221205449970945</v>
       </c>
       <c r="C28">
-        <v>605.392527983572</v>
+        <v>589.2345469932237</v>
       </c>
       <c r="D28">
-        <v>653.788527983572</v>
+        <v>645.7265469932237</v>
       </c>
       <c r="E28">
-        <v>-73.90399999999997</v>
+        <v>-65.80799999999996</v>
       </c>
       <c r="F28">
-        <v>210.496</v>
+        <v>218.592</v>
       </c>
       <c r="G28">
         <v>162.1</v>
@@ -3711,45 +3711,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M28">
-        <v>11.6404288</v>
+        <v>12.6346176</v>
       </c>
       <c r="N28">
-        <v>41.48179342222221</v>
+        <v>40.48760462222221</v>
       </c>
       <c r="O28">
-        <v>4.148179342222221</v>
+        <v>4.048760462222221</v>
       </c>
       <c r="P28">
-        <v>37.33361407999999</v>
+        <v>36.43884415999999</v>
       </c>
       <c r="Q28">
-        <v>56.43361407999999</v>
+        <v>55.53884415999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09278425805216106</v>
+        <v>0.09337897876672528</v>
       </c>
       <c r="T28">
-        <v>0.941736492680067</v>
+        <v>0.9536568724642089</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.1</v>
       </c>
       <c r="W28">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.56359667972216</v>
+        <v>4.204497825262413</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08221205449970945</v>
+        <v>0.08223855804081973</v>
       </c>
       <c r="C29">
-        <v>589.2345469932237</v>
+        <v>580.793620943513</v>
       </c>
       <c r="D29">
-        <v>645.7265469932237</v>
+        <v>645.381620943513</v>
       </c>
       <c r="E29">
-        <v>-65.80799999999996</v>
+        <v>-57.71199999999996</v>
       </c>
       <c r="F29">
-        <v>218.592</v>
+        <v>226.688</v>
       </c>
       <c r="G29">
         <v>162.1</v>
@@ -3793,28 +3793,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M29">
-        <v>12.6346176</v>
+        <v>13.1025664</v>
       </c>
       <c r="N29">
-        <v>40.48760462222221</v>
+        <v>40.01965582222221</v>
       </c>
       <c r="O29">
-        <v>4.048760462222221</v>
+        <v>4.001965582222222</v>
       </c>
       <c r="P29">
-        <v>36.43884415999999</v>
+        <v>36.01769023999999</v>
       </c>
       <c r="Q29">
-        <v>55.53884415999999</v>
+        <v>55.11769023999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09337897876672528</v>
+        <v>0.09399021950113851</v>
       </c>
       <c r="T29">
-        <v>0.9536568724642089</v>
+        <v>0.9659083739090215</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.204497825262413</v>
+        <v>4.054337188645897</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08223855804081973</v>
+        <v>0.08317856158193</v>
       </c>
       <c r="C30">
-        <v>580.793620943513</v>
+        <v>560.6979693806743</v>
       </c>
       <c r="D30">
-        <v>645.381620943513</v>
+        <v>633.3819693806743</v>
       </c>
       <c r="E30">
-        <v>-57.71199999999996</v>
+        <v>-49.61599999999993</v>
       </c>
       <c r="F30">
-        <v>226.688</v>
+        <v>234.784</v>
       </c>
       <c r="G30">
         <v>162.1</v>
@@ -3875,45 +3875,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M30">
-        <v>13.1025664</v>
+        <v>14.3922592</v>
       </c>
       <c r="N30">
-        <v>40.01965582222221</v>
+        <v>38.72996302222221</v>
       </c>
       <c r="O30">
-        <v>4.001965582222222</v>
+        <v>3.872996302222221</v>
       </c>
       <c r="P30">
-        <v>36.01769023999999</v>
+        <v>34.85696671999999</v>
       </c>
       <c r="Q30">
-        <v>55.11769023999999</v>
+        <v>53.95696671999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09399021950113851</v>
+        <v>0.09461867828440844</v>
       </c>
       <c r="T30">
-        <v>0.9659083739090215</v>
+        <v>0.9785049880705894</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.054337188645897</v>
+        <v>3.691027342130011</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08317856158192999</v>
+        <v>0.08323656512304024</v>
       </c>
       <c r="C31">
-        <v>560.6979693806744</v>
+        <v>551.8761228992395</v>
       </c>
       <c r="D31">
-        <v>633.3819693806744</v>
+        <v>632.6561228992394</v>
       </c>
       <c r="E31">
-        <v>-49.61599999999999</v>
+        <v>-41.51999999999998</v>
       </c>
       <c r="F31">
-        <v>234.784</v>
+        <v>242.88</v>
       </c>
       <c r="G31">
         <v>162.1</v>
@@ -3957,28 +3957,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M31">
-        <v>14.3922592</v>
+        <v>14.888544</v>
       </c>
       <c r="N31">
-        <v>38.72996302222221</v>
+        <v>38.23367822222221</v>
       </c>
       <c r="O31">
-        <v>3.872996302222222</v>
+        <v>3.823367822222221</v>
       </c>
       <c r="P31">
-        <v>34.85696672</v>
+        <v>34.41031039999999</v>
       </c>
       <c r="Q31">
-        <v>53.95696672</v>
+        <v>53.51031039999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09461867828440843</v>
+        <v>0.09526509303291464</v>
       </c>
       <c r="T31">
-        <v>0.9785049880705892</v>
+        <v>0.9914615054939161</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.691027342130012</v>
+        <v>3.567993097392345</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08323656512304024</v>
+        <v>0.08407576866415054</v>
       </c>
       <c r="C32">
-        <v>551.8761228992395</v>
+        <v>533.4615909320221</v>
       </c>
       <c r="D32">
-        <v>632.6561228992394</v>
+        <v>622.3375909320221</v>
       </c>
       <c r="E32">
-        <v>-41.51999999999998</v>
+        <v>-33.42399999999998</v>
       </c>
       <c r="F32">
-        <v>242.88</v>
+        <v>250.976</v>
       </c>
       <c r="G32">
         <v>162.1</v>
@@ -4039,45 +4039,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M32">
-        <v>14.888544</v>
+        <v>16.0875616</v>
       </c>
       <c r="N32">
-        <v>38.23367822222221</v>
+        <v>37.03466062222221</v>
       </c>
       <c r="O32">
-        <v>3.823367822222221</v>
+        <v>3.703466062222221</v>
       </c>
       <c r="P32">
-        <v>34.41031039999999</v>
+        <v>33.33119455999999</v>
       </c>
       <c r="Q32">
-        <v>53.51031039999999</v>
+        <v>52.43119455999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09526509303291464</v>
+        <v>0.09593024444079787</v>
       </c>
       <c r="T32">
-        <v>0.9914615054939161</v>
+        <v>1.004793574146905</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.567993097392345</v>
+        <v>3.302067991598069</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08407576866415054</v>
+        <v>0.08415897220526078</v>
       </c>
       <c r="C33">
-        <v>533.4615909320221</v>
+        <v>524.3608617313505</v>
       </c>
       <c r="D33">
-        <v>622.3375909320221</v>
+        <v>621.3328617313505</v>
       </c>
       <c r="E33">
-        <v>-33.42399999999998</v>
+        <v>-25.32799999999997</v>
       </c>
       <c r="F33">
-        <v>250.976</v>
+        <v>259.072</v>
       </c>
       <c r="G33">
         <v>162.1</v>
@@ -4121,28 +4121,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M33">
-        <v>16.0875616</v>
+        <v>16.6065152</v>
       </c>
       <c r="N33">
-        <v>37.03466062222221</v>
+        <v>36.51570702222222</v>
       </c>
       <c r="O33">
-        <v>3.703466062222221</v>
+        <v>3.651570702222222</v>
       </c>
       <c r="P33">
-        <v>33.33119455999999</v>
+        <v>32.86413631999999</v>
       </c>
       <c r="Q33">
-        <v>52.43119455999999</v>
+        <v>51.96413631999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09593024444079787</v>
+        <v>0.09661495912538351</v>
       </c>
       <c r="T33">
-        <v>1.004793574146905</v>
+        <v>1.018517762466158</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.302067991598069</v>
+        <v>3.198878366860629</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08415897220526078</v>
+        <v>0.08424217574637106</v>
       </c>
       <c r="C34">
-        <v>524.3608617313505</v>
+        <v>515.2633714597039</v>
       </c>
       <c r="D34">
-        <v>621.3328617313505</v>
+        <v>620.3313714597039</v>
       </c>
       <c r="E34">
-        <v>-25.32799999999997</v>
+        <v>-17.23199999999997</v>
       </c>
       <c r="F34">
-        <v>259.072</v>
+        <v>267.168</v>
       </c>
       <c r="G34">
         <v>162.1</v>
@@ -4203,28 +4203,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M34">
-        <v>16.6065152</v>
+        <v>17.1254688</v>
       </c>
       <c r="N34">
-        <v>36.51570702222222</v>
+        <v>35.99675342222221</v>
       </c>
       <c r="O34">
-        <v>3.651570702222222</v>
+        <v>3.599675342222222</v>
       </c>
       <c r="P34">
-        <v>32.86413631999999</v>
+        <v>32.39707807999999</v>
       </c>
       <c r="Q34">
-        <v>51.96413631999999</v>
+        <v>51.49707807999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09661495912538351</v>
+        <v>0.09732011305428517</v>
       </c>
       <c r="T34">
-        <v>1.018517762466158</v>
+        <v>1.032651628048672</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.198878366860629</v>
+        <v>3.101942658773943</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08424217574637106</v>
+        <v>0.08432537928748132</v>
       </c>
       <c r="C35">
-        <v>515.2633714597039</v>
+        <v>506.1691044803632</v>
       </c>
       <c r="D35">
-        <v>620.3313714597039</v>
+        <v>619.3331044803632</v>
       </c>
       <c r="E35">
-        <v>-17.23199999999997</v>
+        <v>-9.135999999999967</v>
       </c>
       <c r="F35">
-        <v>267.168</v>
+        <v>275.264</v>
       </c>
       <c r="G35">
         <v>162.1</v>
@@ -4285,28 +4285,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M35">
-        <v>17.1254688</v>
+        <v>17.6444224</v>
       </c>
       <c r="N35">
-        <v>35.99675342222221</v>
+        <v>35.47779982222221</v>
       </c>
       <c r="O35">
-        <v>3.599675342222222</v>
+        <v>3.547779982222221</v>
       </c>
       <c r="P35">
-        <v>32.39707807999999</v>
+        <v>31.93001983999999</v>
       </c>
       <c r="Q35">
-        <v>51.49707807999999</v>
+        <v>51.03001983999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09732011305428517</v>
+        <v>0.09804663528406263</v>
       </c>
       <c r="T35">
-        <v>1.032651628048672</v>
+        <v>1.047213792588232</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.101942658773943</v>
+        <v>3.010709051162944</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08432537928748132</v>
+        <v>0.08686558282859158</v>
       </c>
       <c r="C36">
-        <v>506.1691044803632</v>
+        <v>469.0699977721523</v>
       </c>
       <c r="D36">
-        <v>619.3331044803632</v>
+        <v>590.3299977721523</v>
       </c>
       <c r="E36">
-        <v>-9.135999999999967</v>
+        <v>-1.039999999999964</v>
       </c>
       <c r="F36">
-        <v>275.264</v>
+        <v>283.36</v>
       </c>
       <c r="G36">
         <v>162.1</v>
@@ -4367,45 +4367,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M36">
-        <v>17.6444224</v>
+        <v>20.373584</v>
       </c>
       <c r="N36">
-        <v>35.47779982222221</v>
+        <v>32.74863822222221</v>
       </c>
       <c r="O36">
-        <v>3.547779982222221</v>
+        <v>3.274863822222221</v>
       </c>
       <c r="P36">
-        <v>31.93001983999999</v>
+        <v>29.47377439999999</v>
       </c>
       <c r="Q36">
-        <v>51.03001983999999</v>
+        <v>48.57377439999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09804663528406263</v>
+        <v>0.09879551204398707</v>
       </c>
       <c r="T36">
-        <v>1.047213792588232</v>
+        <v>1.062224023729009</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.010709051162944</v>
+        <v>2.607406837315526</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08686558282859158</v>
+        <v>0.08701898636970185</v>
       </c>
       <c r="C37">
-        <v>469.0699977721523</v>
+        <v>459.3092230491155</v>
       </c>
       <c r="D37">
-        <v>590.3299977721523</v>
+        <v>588.6652230491155</v>
       </c>
       <c r="E37">
-        <v>-1.039999999999964</v>
+        <v>7.05600000000004</v>
       </c>
       <c r="F37">
-        <v>283.36</v>
+        <v>291.456</v>
       </c>
       <c r="G37">
         <v>162.1</v>
@@ -4449,28 +4449,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M37">
-        <v>20.373584</v>
+        <v>20.9556864</v>
       </c>
       <c r="N37">
-        <v>32.74863822222221</v>
+        <v>32.16653582222222</v>
       </c>
       <c r="O37">
-        <v>3.274863822222221</v>
+        <v>3.216653582222222</v>
       </c>
       <c r="P37">
-        <v>29.47377439999999</v>
+        <v>28.94988223999999</v>
       </c>
       <c r="Q37">
-        <v>48.57377439999999</v>
+        <v>48.04988224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09879551204398707</v>
+        <v>0.09956779120265916</v>
       </c>
       <c r="T37">
-        <v>1.062224023729009</v>
+        <v>1.077703324592936</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.607406837315526</v>
+        <v>2.534978869612317</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08701898636970186</v>
+        <v>0.08847108991081212</v>
       </c>
       <c r="C38">
-        <v>459.3092230491154</v>
+        <v>435.907637911129</v>
       </c>
       <c r="D38">
-        <v>588.6652230491154</v>
+        <v>573.359637911129</v>
       </c>
       <c r="E38">
-        <v>7.05600000000004</v>
+        <v>15.15200000000004</v>
       </c>
       <c r="F38">
-        <v>291.456</v>
+        <v>299.552</v>
       </c>
       <c r="G38">
         <v>162.1</v>
@@ -4531,45 +4531,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M38">
-        <v>20.9556864</v>
+        <v>22.7060416</v>
       </c>
       <c r="N38">
-        <v>32.16653582222222</v>
+        <v>30.41618062222221</v>
       </c>
       <c r="O38">
-        <v>3.216653582222222</v>
+        <v>3.041618062222221</v>
       </c>
       <c r="P38">
-        <v>28.94988223999999</v>
+        <v>27.37456255999999</v>
       </c>
       <c r="Q38">
-        <v>48.04988224</v>
+        <v>46.47456256</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09956779120265916</v>
+        <v>0.1003645871600193</v>
       </c>
       <c r="T38">
-        <v>1.077703324592936</v>
+        <v>1.093674031833495</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.1</v>
       </c>
       <c r="W38">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.534978869612317</v>
+        <v>2.339563326714869</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08847108991081212</v>
+        <v>0.0886595934519224</v>
       </c>
       <c r="C39">
-        <v>435.907637911129</v>
+        <v>425.882926598515</v>
       </c>
       <c r="D39">
-        <v>573.359637911129</v>
+        <v>571.430926598515</v>
       </c>
       <c r="E39">
-        <v>15.15200000000004</v>
+        <v>23.24800000000005</v>
       </c>
       <c r="F39">
-        <v>299.552</v>
+        <v>307.648</v>
       </c>
       <c r="G39">
         <v>162.1</v>
@@ -4613,28 +4613,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M39">
-        <v>22.7060416</v>
+        <v>23.3197184</v>
       </c>
       <c r="N39">
-        <v>30.41618062222221</v>
+        <v>29.80250382222221</v>
       </c>
       <c r="O39">
-        <v>3.041618062222221</v>
+        <v>2.980250382222221</v>
       </c>
       <c r="P39">
-        <v>27.37456255999999</v>
+        <v>26.82225343999999</v>
       </c>
       <c r="Q39">
-        <v>46.47456256</v>
+        <v>45.92225343999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1003645871600193</v>
+        <v>0.1011870862127781</v>
       </c>
       <c r="T39">
-        <v>1.093674031833495</v>
+        <v>1.110159923178589</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.339563326714869</v>
+        <v>2.277995870748688</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0886595934519224</v>
+        <v>0.08884809699303266</v>
       </c>
       <c r="C40">
-        <v>425.882926598515</v>
+        <v>415.8711476782656</v>
       </c>
       <c r="D40">
-        <v>571.430926598515</v>
+        <v>569.5151476782656</v>
       </c>
       <c r="E40">
-        <v>23.24800000000005</v>
+        <v>31.34400000000005</v>
       </c>
       <c r="F40">
-        <v>307.648</v>
+        <v>315.744</v>
       </c>
       <c r="G40">
         <v>162.1</v>
@@ -4695,28 +4695,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M40">
-        <v>23.3197184</v>
+        <v>23.9333952</v>
       </c>
       <c r="N40">
-        <v>29.80250382222221</v>
+        <v>29.18882702222221</v>
       </c>
       <c r="O40">
-        <v>2.980250382222221</v>
+        <v>2.918882702222221</v>
       </c>
       <c r="P40">
-        <v>26.82225343999999</v>
+        <v>26.26994431999999</v>
       </c>
       <c r="Q40">
-        <v>45.92225343999999</v>
+        <v>45.36994431999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1011870862127781</v>
+        <v>0.1020365524475945</v>
       </c>
       <c r="T40">
-        <v>1.110159923178589</v>
+        <v>1.12718633555139</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.277995870748688</v>
+        <v>2.219585720216671</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08884809699303266</v>
+        <v>0.08903660053414293</v>
       </c>
       <c r="C41">
-        <v>415.8711476782656</v>
+        <v>405.8721715136121</v>
       </c>
       <c r="D41">
-        <v>569.5151476782656</v>
+        <v>567.6121715136121</v>
       </c>
       <c r="E41">
-        <v>31.34400000000005</v>
+        <v>39.44000000000005</v>
       </c>
       <c r="F41">
-        <v>315.744</v>
+        <v>323.84</v>
       </c>
       <c r="G41">
         <v>162.1</v>
@@ -4777,28 +4777,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M41">
-        <v>23.9333952</v>
+        <v>24.547072</v>
       </c>
       <c r="N41">
-        <v>29.18882702222221</v>
+        <v>28.57515022222221</v>
       </c>
       <c r="O41">
-        <v>2.918882702222221</v>
+        <v>2.857515022222221</v>
       </c>
       <c r="P41">
-        <v>26.26994431999999</v>
+        <v>25.71763519999999</v>
       </c>
       <c r="Q41">
-        <v>45.36994431999999</v>
+        <v>44.81763519999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1020365524475945</v>
+        <v>0.1029143342235715</v>
       </c>
       <c r="T41">
-        <v>1.12718633555139</v>
+        <v>1.144780295003285</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.219585720216671</v>
+        <v>2.164096077211254</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08903660053414293</v>
+        <v>0.08922510407525321</v>
       </c>
       <c r="C42">
-        <v>405.8721715136121</v>
+        <v>395.8858701946875</v>
       </c>
       <c r="D42">
-        <v>567.6121715136121</v>
+        <v>565.7218701946875</v>
       </c>
       <c r="E42">
-        <v>39.44000000000005</v>
+        <v>47.53600000000006</v>
       </c>
       <c r="F42">
-        <v>323.84</v>
+        <v>331.936</v>
       </c>
       <c r="G42">
         <v>162.1</v>
@@ -4859,28 +4859,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M42">
-        <v>24.547072</v>
+        <v>25.1607488</v>
       </c>
       <c r="N42">
-        <v>28.57515022222221</v>
+        <v>27.96147342222221</v>
       </c>
       <c r="O42">
-        <v>2.857515022222221</v>
+        <v>2.796147342222221</v>
       </c>
       <c r="P42">
-        <v>25.71763519999999</v>
+        <v>25.16532607999999</v>
       </c>
       <c r="Q42">
-        <v>44.81763519999999</v>
+        <v>44.26532607999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1029143342235715</v>
+        <v>0.1038218713139885</v>
       </c>
       <c r="T42">
-        <v>1.144780295003285</v>
+        <v>1.162970659860328</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.164096077211254</v>
+        <v>2.11131324605976</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08922510407525321</v>
+        <v>0.08941360761636347</v>
       </c>
       <c r="C43">
-        <v>395.8858701946875</v>
+        <v>385.9121175098668</v>
       </c>
       <c r="D43">
-        <v>565.7218701946875</v>
+        <v>563.8441175098668</v>
       </c>
       <c r="E43">
-        <v>47.53600000000006</v>
+        <v>55.63200000000006</v>
       </c>
       <c r="F43">
-        <v>331.936</v>
+        <v>340.032</v>
       </c>
       <c r="G43">
         <v>162.1</v>
@@ -4941,28 +4941,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M43">
-        <v>25.1607488</v>
+        <v>25.7744256</v>
       </c>
       <c r="N43">
-        <v>27.96147342222221</v>
+        <v>27.34779662222221</v>
       </c>
       <c r="O43">
-        <v>2.796147342222221</v>
+        <v>2.734779662222221</v>
       </c>
       <c r="P43">
-        <v>25.16532607999999</v>
+        <v>24.61301695999999</v>
       </c>
       <c r="Q43">
-        <v>44.26532607999999</v>
+        <v>43.71301695999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1038218713139885</v>
+        <v>0.1047607027868336</v>
       </c>
       <c r="T43">
-        <v>1.162970659860328</v>
+        <v>1.18178827867796</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.11131324605976</v>
+        <v>2.061043883058337</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08941360761636347</v>
+        <v>0.08960211115747374</v>
       </c>
       <c r="C44">
-        <v>385.9121175098668</v>
+        <v>375.9507889176747</v>
       </c>
       <c r="D44">
-        <v>563.8441175098668</v>
+        <v>561.9787889176747</v>
       </c>
       <c r="E44">
-        <v>55.63200000000001</v>
+        <v>63.72800000000001</v>
       </c>
       <c r="F44">
-        <v>340.032</v>
+        <v>348.128</v>
       </c>
       <c r="G44">
         <v>162.1</v>
@@ -5023,28 +5023,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M44">
-        <v>25.7744256</v>
+        <v>26.3881024</v>
       </c>
       <c r="N44">
-        <v>27.34779662222221</v>
+        <v>26.73411982222221</v>
       </c>
       <c r="O44">
-        <v>2.734779662222222</v>
+        <v>2.673411982222222</v>
       </c>
       <c r="P44">
-        <v>24.61301695999999</v>
+        <v>24.06070783999999</v>
       </c>
       <c r="Q44">
-        <v>43.71301695999999</v>
+        <v>43.16070783999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1047607027868336</v>
+        <v>0.1057324757148662</v>
       </c>
       <c r="T44">
-        <v>1.18178827867796</v>
+        <v>1.201266164822526</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.061043883058337</v>
+        <v>2.013112629963957</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08960211115747374</v>
+        <v>0.09541381469858401</v>
       </c>
       <c r="C45">
-        <v>375.9507889176747</v>
+        <v>315.840770402186</v>
       </c>
       <c r="D45">
-        <v>561.9787889176747</v>
+        <v>509.964770402186</v>
       </c>
       <c r="E45">
-        <v>63.72800000000001</v>
+        <v>71.82400000000001</v>
       </c>
       <c r="F45">
-        <v>348.128</v>
+        <v>356.224</v>
       </c>
       <c r="G45">
         <v>162.1</v>
@@ -5105,45 +5105,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M45">
-        <v>26.3881024</v>
+        <v>32.06016</v>
       </c>
       <c r="N45">
-        <v>26.73411982222221</v>
+        <v>21.06206222222222</v>
       </c>
       <c r="O45">
-        <v>2.673411982222222</v>
+        <v>2.106206222222222</v>
       </c>
       <c r="P45">
-        <v>24.06070783999999</v>
+        <v>18.95585599999999</v>
       </c>
       <c r="Q45">
-        <v>43.16070783999999</v>
+        <v>38.05585599999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1057324757148662</v>
+        <v>0.1067389548189</v>
       </c>
       <c r="T45">
-        <v>1.201266164822526</v>
+        <v>1.221439689757969</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.013112629963957</v>
+        <v>1.656954370228415</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09541381469858401</v>
+        <v>0.09573011823969428</v>
       </c>
       <c r="C46">
-        <v>315.840770402186</v>
+        <v>305.18878091094</v>
       </c>
       <c r="D46">
-        <v>509.964770402186</v>
+        <v>507.40878091094</v>
       </c>
       <c r="E46">
-        <v>71.82400000000001</v>
+        <v>79.92000000000002</v>
       </c>
       <c r="F46">
-        <v>356.224</v>
+        <v>364.32</v>
       </c>
       <c r="G46">
         <v>162.1</v>
@@ -5187,28 +5187,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M46">
-        <v>32.06016</v>
+        <v>32.78879999999999</v>
       </c>
       <c r="N46">
-        <v>21.06206222222222</v>
+        <v>20.33342222222222</v>
       </c>
       <c r="O46">
-        <v>2.106206222222222</v>
+        <v>2.033342222222222</v>
       </c>
       <c r="P46">
-        <v>18.95585599999999</v>
+        <v>18.30008</v>
       </c>
       <c r="Q46">
-        <v>38.05585599999999</v>
+        <v>37.40008</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1067389548189</v>
+        <v>0.1077820331630805</v>
       </c>
       <c r="T46">
-        <v>1.221439689757969</v>
+        <v>1.242346797418337</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.656954370228415</v>
+        <v>1.620133162001117</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09573011823969428</v>
+        <v>0.09604642178080454</v>
       </c>
       <c r="C47">
-        <v>305.18878091094</v>
+        <v>294.5622853422454</v>
       </c>
       <c r="D47">
-        <v>507.40878091094</v>
+        <v>504.8782853422455</v>
       </c>
       <c r="E47">
-        <v>79.92000000000002</v>
+        <v>88.01600000000008</v>
       </c>
       <c r="F47">
-        <v>364.32</v>
+        <v>372.4160000000001</v>
       </c>
       <c r="G47">
         <v>162.1</v>
@@ -5269,28 +5269,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M47">
-        <v>32.78879999999999</v>
+        <v>33.51744</v>
       </c>
       <c r="N47">
-        <v>20.33342222222222</v>
+        <v>19.60478222222221</v>
       </c>
       <c r="O47">
-        <v>2.033342222222222</v>
+        <v>1.960478222222221</v>
       </c>
       <c r="P47">
-        <v>18.30008</v>
+        <v>17.64430399999999</v>
       </c>
       <c r="Q47">
-        <v>37.40008</v>
+        <v>36.74430399999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1077820331630805</v>
+        <v>0.1088637440385269</v>
       </c>
       <c r="T47">
-        <v>1.242346797418337</v>
+        <v>1.26402824239946</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.620133162001117</v>
+        <v>1.584912875870657</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09604642178080454</v>
+        <v>0.09636272532191481</v>
       </c>
       <c r="C48">
-        <v>294.5622853422454</v>
+        <v>283.9609041670426</v>
       </c>
       <c r="D48">
-        <v>504.8782853422455</v>
+        <v>502.3729041670426</v>
       </c>
       <c r="E48">
-        <v>88.01600000000008</v>
+        <v>96.11200000000008</v>
       </c>
       <c r="F48">
-        <v>372.4160000000001</v>
+        <v>380.5120000000001</v>
       </c>
       <c r="G48">
         <v>162.1</v>
@@ -5351,28 +5351,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M48">
-        <v>33.51744</v>
+        <v>34.24608000000001</v>
       </c>
       <c r="N48">
-        <v>19.60478222222221</v>
+        <v>18.87614222222221</v>
       </c>
       <c r="O48">
-        <v>1.960478222222221</v>
+        <v>1.887614222222221</v>
       </c>
       <c r="P48">
-        <v>17.64430399999999</v>
+        <v>16.98852799999998</v>
       </c>
       <c r="Q48">
-        <v>36.74430399999999</v>
+        <v>36.08852799999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1088637440385269</v>
+        <v>0.1099862741922921</v>
       </c>
       <c r="T48">
-        <v>1.26402824239946</v>
+        <v>1.28652785511572</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.584912875870657</v>
+        <v>1.551191325320218</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09636272532191481</v>
+        <v>0.09667902886302508</v>
       </c>
       <c r="C49">
-        <v>283.9609041670426</v>
+        <v>273.384265352492</v>
       </c>
       <c r="D49">
-        <v>502.3729041670426</v>
+        <v>499.8922653524921</v>
       </c>
       <c r="E49">
-        <v>96.11200000000008</v>
+        <v>104.2080000000001</v>
       </c>
       <c r="F49">
-        <v>380.5120000000001</v>
+        <v>388.6080000000001</v>
       </c>
       <c r="G49">
         <v>162.1</v>
@@ -5433,28 +5433,28 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M49">
-        <v>34.24608000000001</v>
+        <v>34.97472</v>
       </c>
       <c r="N49">
-        <v>18.87614222222221</v>
+        <v>18.14750222222221</v>
       </c>
       <c r="O49">
-        <v>1.887614222222221</v>
+        <v>1.814750222222221</v>
       </c>
       <c r="P49">
-        <v>16.98852799999998</v>
+        <v>16.33275199999999</v>
       </c>
       <c r="Q49">
-        <v>36.08852799999998</v>
+        <v>35.43275199999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1099862741922921</v>
+        <v>0.1111519785827405</v>
       </c>
       <c r="T49">
-        <v>1.28652785511572</v>
+        <v>1.309892837551835</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.551191325320218</v>
+        <v>1.518874839376047</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09667902886302507</v>
+        <v>0.1228293901688203</v>
       </c>
       <c r="C50">
-        <v>273.3842653524923</v>
+        <v>120.373700071947</v>
       </c>
       <c r="D50">
-        <v>499.8922653524922</v>
+        <v>354.977700071947</v>
       </c>
       <c r="E50">
-        <v>104.208</v>
+        <v>112.304</v>
       </c>
       <c r="F50">
-        <v>388.608</v>
+        <v>396.704</v>
       </c>
       <c r="G50">
         <v>162.1</v>
@@ -5515,45 +5515,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M50">
-        <v>34.97472</v>
+        <v>58.2361472</v>
       </c>
       <c r="N50">
-        <v>18.14750222222222</v>
+        <v>-5.113924977777792</v>
       </c>
       <c r="O50">
-        <v>1.814750222222222</v>
+        <v>-0.5113924977777792</v>
       </c>
       <c r="P50">
-        <v>16.33275199999999</v>
+        <v>-4.602532480000013</v>
       </c>
       <c r="Q50">
-        <v>35.43275199999999</v>
+        <v>14.49746751999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1111519785827405</v>
+        <v>0.1126645675978918</v>
       </c>
       <c r="T50">
-        <v>1.309892837551835</v>
+        <v>1.340210657456826</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1</v>
+        <v>0.09121864130156984</v>
       </c>
       <c r="W50">
-        <v>0.081</v>
+        <v>0.1334091034569296</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.518874839376047</v>
+        <v>0.9121864130156984</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1228293901688203</v>
+        <v>0.1238393901688203</v>
       </c>
       <c r="C51">
-        <v>120.373700071947</v>
+        <v>108.3472267949011</v>
       </c>
       <c r="D51">
-        <v>354.977700071947</v>
+        <v>351.0472267949011</v>
       </c>
       <c r="E51">
-        <v>112.304</v>
+        <v>120.4</v>
       </c>
       <c r="F51">
-        <v>396.704</v>
+        <v>404.8</v>
       </c>
       <c r="G51">
         <v>162.1</v>
@@ -5597,37 +5597,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M51">
-        <v>58.2361472</v>
+        <v>59.42464000000001</v>
       </c>
       <c r="N51">
-        <v>-5.113924977777792</v>
+        <v>-6.302417777777798</v>
       </c>
       <c r="O51">
-        <v>-0.5113924977777792</v>
+        <v>-0.6302417777777798</v>
       </c>
       <c r="P51">
-        <v>-4.602532480000013</v>
+        <v>-5.672176000000018</v>
       </c>
       <c r="Q51">
-        <v>14.49746751999999</v>
+        <v>13.42782399999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1126645675978918</v>
+        <v>0.1140018589498497</v>
       </c>
       <c r="T51">
-        <v>1.340210657456826</v>
+        <v>1.367014870605962</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.09121864130156984</v>
+        <v>0.08939426847553844</v>
       </c>
       <c r="W51">
-        <v>0.1334091034569296</v>
+        <v>0.133676921387791</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9121864130156984</v>
+        <v>0.8939426847553844</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1238393901688203</v>
+        <v>0.1248493901688203</v>
       </c>
       <c r="C52">
-        <v>108.3472267949011</v>
+        <v>96.40684027390461</v>
       </c>
       <c r="D52">
-        <v>351.0472267949011</v>
+        <v>347.2028402739046</v>
       </c>
       <c r="E52">
-        <v>120.4</v>
+        <v>128.496</v>
       </c>
       <c r="F52">
-        <v>404.8</v>
+        <v>412.896</v>
       </c>
       <c r="G52">
         <v>162.1</v>
@@ -5679,37 +5679,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M52">
-        <v>59.42464000000001</v>
+        <v>60.61313280000001</v>
       </c>
       <c r="N52">
-        <v>-6.302417777777798</v>
+        <v>-7.490910577777797</v>
       </c>
       <c r="O52">
-        <v>-0.6302417777777798</v>
+        <v>-0.7490910577777797</v>
       </c>
       <c r="P52">
-        <v>-5.672176000000018</v>
+        <v>-6.741819520000017</v>
       </c>
       <c r="Q52">
-        <v>13.42782399999998</v>
+        <v>12.35818047999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1140018589498497</v>
+        <v>0.1153937336222956</v>
       </c>
       <c r="T52">
-        <v>1.367014870605962</v>
+        <v>1.39491313327139</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.08939426847553844</v>
+        <v>0.08764143968190043</v>
       </c>
       <c r="W52">
-        <v>0.133676921387791</v>
+        <v>0.133934236654697</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8939426847553844</v>
+        <v>0.8764143968190043</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1248493901688203</v>
+        <v>0.1258593901688203</v>
       </c>
       <c r="C53">
-        <v>96.40684027390461</v>
+        <v>84.54974288777788</v>
       </c>
       <c r="D53">
-        <v>347.2028402739046</v>
+        <v>343.4417428877779</v>
       </c>
       <c r="E53">
-        <v>128.496</v>
+        <v>136.592</v>
       </c>
       <c r="F53">
-        <v>412.896</v>
+        <v>420.992</v>
       </c>
       <c r="G53">
         <v>162.1</v>
@@ -5761,37 +5761,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M53">
-        <v>60.61313280000001</v>
+        <v>61.80162560000001</v>
       </c>
       <c r="N53">
-        <v>-7.490910577777797</v>
+        <v>-8.679403377777795</v>
       </c>
       <c r="O53">
-        <v>-0.7490910577777797</v>
+        <v>-0.8679403377777796</v>
       </c>
       <c r="P53">
-        <v>-6.741819520000017</v>
+        <v>-7.811463040000016</v>
       </c>
       <c r="Q53">
-        <v>12.35818047999998</v>
+        <v>11.28853695999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1153937336222956</v>
+        <v>0.1168436030727601</v>
       </c>
       <c r="T53">
-        <v>1.39491313327139</v>
+        <v>1.423973823547877</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.08764143968190043</v>
+        <v>0.08595602738032543</v>
       </c>
       <c r="W53">
-        <v>0.133934236654697</v>
+        <v>0.1341816551805682</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8764143968190043</v>
+        <v>0.8595602738032542</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1258593901688203</v>
+        <v>0.1268693901688203</v>
       </c>
       <c r="C54">
-        <v>84.54974288777788</v>
+        <v>72.77325693792699</v>
       </c>
       <c r="D54">
-        <v>343.4417428877779</v>
+        <v>339.761256937927</v>
       </c>
       <c r="E54">
-        <v>136.592</v>
+        <v>144.688</v>
       </c>
       <c r="F54">
-        <v>420.992</v>
+        <v>429.088</v>
       </c>
       <c r="G54">
         <v>162.1</v>
@@ -5843,37 +5843,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M54">
-        <v>61.80162560000001</v>
+        <v>62.99011840000001</v>
       </c>
       <c r="N54">
-        <v>-8.679403377777795</v>
+        <v>-9.867896177777794</v>
       </c>
       <c r="O54">
-        <v>-0.8679403377777796</v>
+        <v>-0.9867896177777795</v>
       </c>
       <c r="P54">
-        <v>-7.811463040000016</v>
+        <v>-8.881106560000015</v>
       </c>
       <c r="Q54">
-        <v>11.28853695999999</v>
+        <v>10.21889343999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1168436030727601</v>
+        <v>0.1183551690955848</v>
       </c>
       <c r="T54">
-        <v>1.423973823547877</v>
+        <v>1.454271138942513</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.08595602738032543</v>
+        <v>0.08433421554296079</v>
       </c>
       <c r="W54">
-        <v>0.1341816551805682</v>
+        <v>0.1344197371582934</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8595602738032542</v>
+        <v>0.8433421554296079</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1268693901688203</v>
+        <v>0.1278793901688203</v>
       </c>
       <c r="C55">
-        <v>72.77325693792699</v>
+        <v>61.07481829073623</v>
       </c>
       <c r="D55">
-        <v>339.761256937927</v>
+        <v>336.1588182907362</v>
       </c>
       <c r="E55">
-        <v>144.688</v>
+        <v>152.784</v>
       </c>
       <c r="F55">
-        <v>429.088</v>
+        <v>437.184</v>
       </c>
       <c r="G55">
         <v>162.1</v>
@@ -5925,37 +5925,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M55">
-        <v>62.99011840000001</v>
+        <v>64.17861120000001</v>
       </c>
       <c r="N55">
-        <v>-9.867896177777794</v>
+        <v>-11.05638897777779</v>
       </c>
       <c r="O55">
-        <v>-0.9867896177777795</v>
+        <v>-1.105638897777779</v>
       </c>
       <c r="P55">
-        <v>-8.881106560000015</v>
+        <v>-9.950750080000013</v>
       </c>
       <c r="Q55">
-        <v>10.21889343999999</v>
+        <v>9.149249919999988</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1183551690955848</v>
+        <v>0.1199324553802714</v>
       </c>
       <c r="T55">
-        <v>1.454271138942513</v>
+        <v>1.485885728919524</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.08433421554296079</v>
+        <v>0.08277247081068374</v>
       </c>
       <c r="W55">
-        <v>0.1344197371582934</v>
+        <v>0.1346490012849916</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8433421554296079</v>
+        <v>0.8277247081068374</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1278793901688203</v>
+        <v>0.1288893901688203</v>
       </c>
       <c r="C56">
-        <v>61.07481829073623</v>
+        <v>49.45197042016883</v>
       </c>
       <c r="D56">
-        <v>336.1588182907362</v>
+        <v>332.6319704201688</v>
       </c>
       <c r="E56">
-        <v>152.784</v>
+        <v>160.8800000000001</v>
       </c>
       <c r="F56">
-        <v>437.184</v>
+        <v>445.28</v>
       </c>
       <c r="G56">
         <v>162.1</v>
@@ -6007,37 +6007,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M56">
-        <v>64.17861120000001</v>
+        <v>65.36710400000001</v>
       </c>
       <c r="N56">
-        <v>-11.05638897777779</v>
+        <v>-12.2448817777778</v>
       </c>
       <c r="O56">
-        <v>-1.105638897777779</v>
+        <v>-1.22448817777778</v>
       </c>
       <c r="P56">
-        <v>-9.950750080000013</v>
+        <v>-11.02039360000002</v>
       </c>
       <c r="Q56">
-        <v>9.149249919999988</v>
+        <v>8.079606399999982</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1199324553802714</v>
+        <v>0.1215798432776108</v>
       </c>
       <c r="T56">
-        <v>1.485885728919524</v>
+        <v>1.518905411784403</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.08277247081068374</v>
+        <v>0.08126751679594403</v>
       </c>
       <c r="W56">
-        <v>0.1346490012849916</v>
+        <v>0.1348699285343554</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8277247081068374</v>
+        <v>0.8126751679594403</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1288893901688203</v>
+        <v>0.1605684668042765</v>
       </c>
       <c r="C57">
-        <v>49.45197042016883</v>
+        <v>-41.00249346675542</v>
       </c>
       <c r="D57">
-        <v>332.6319704201688</v>
+        <v>250.2735065332446</v>
       </c>
       <c r="E57">
-        <v>160.8800000000001</v>
+        <v>168.9760000000001</v>
       </c>
       <c r="F57">
-        <v>445.28</v>
+        <v>453.376</v>
       </c>
       <c r="G57">
         <v>162.1</v>
@@ -6089,45 +6089,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M57">
-        <v>65.36710400000001</v>
+        <v>91.0379008</v>
       </c>
       <c r="N57">
-        <v>-12.2448817777778</v>
+        <v>-37.91567857777779</v>
       </c>
       <c r="O57">
-        <v>-1.22448817777778</v>
+        <v>-3.791567857777779</v>
       </c>
       <c r="P57">
-        <v>-11.02039360000002</v>
+        <v>-34.12411072000001</v>
       </c>
       <c r="Q57">
-        <v>8.079606399999982</v>
+        <v>-15.02411072000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1215798432776108</v>
+        <v>0.1242772866145023</v>
       </c>
       <c r="T57">
-        <v>1.518905411784403</v>
+        <v>1.572972048836908</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08126751679594403</v>
+        <v>0.05835176531467454</v>
       </c>
       <c r="W57">
-        <v>0.1348699285343554</v>
+        <v>0.1890829655248134</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8126751679594403</v>
+        <v>0.5835176531467454</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1605684668042765</v>
+        <v>0.1621184668042765</v>
       </c>
       <c r="C58">
-        <v>-41.00249346675542</v>
+        <v>-52.09412704035816</v>
       </c>
       <c r="D58">
-        <v>250.2735065332446</v>
+        <v>247.2778729596419</v>
       </c>
       <c r="E58">
-        <v>168.9760000000001</v>
+        <v>177.0720000000001</v>
       </c>
       <c r="F58">
-        <v>453.376</v>
+        <v>461.472</v>
       </c>
       <c r="G58">
         <v>162.1</v>
@@ -6171,37 +6171,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M58">
-        <v>91.0379008</v>
+        <v>92.66357760000001</v>
       </c>
       <c r="N58">
-        <v>-37.91567857777779</v>
+        <v>-39.5413553777778</v>
       </c>
       <c r="O58">
-        <v>-3.791567857777779</v>
+        <v>-3.95413553777778</v>
       </c>
       <c r="P58">
-        <v>-34.12411072000001</v>
+        <v>-35.58721984000002</v>
       </c>
       <c r="Q58">
-        <v>-15.02411072000001</v>
+        <v>-16.48721984000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1242772866145023</v>
+        <v>0.1261023397915838</v>
       </c>
       <c r="T58">
-        <v>1.572972048836908</v>
+        <v>1.609552794158697</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.05835176531467454</v>
+        <v>0.05732805013371533</v>
       </c>
       <c r="W58">
-        <v>0.1890829655248134</v>
+        <v>0.18928852753315</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5835176531467454</v>
+        <v>0.5732805013371534</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1621184668042765</v>
+        <v>0.1636684668042765</v>
       </c>
       <c r="C59">
-        <v>-52.09412704035816</v>
+        <v>-63.11489670607602</v>
       </c>
       <c r="D59">
-        <v>247.2778729596419</v>
+        <v>244.3531032939241</v>
       </c>
       <c r="E59">
-        <v>177.0720000000001</v>
+        <v>185.1680000000001</v>
       </c>
       <c r="F59">
-        <v>461.472</v>
+        <v>469.5680000000001</v>
       </c>
       <c r="G59">
         <v>162.1</v>
@@ -6253,37 +6253,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M59">
-        <v>92.66357760000001</v>
+        <v>94.28925440000002</v>
       </c>
       <c r="N59">
-        <v>-39.5413553777778</v>
+        <v>-41.16703217777781</v>
       </c>
       <c r="O59">
-        <v>-3.95413553777778</v>
+        <v>-4.116703217777781</v>
       </c>
       <c r="P59">
-        <v>-35.58721984000002</v>
+        <v>-37.05032896000002</v>
       </c>
       <c r="Q59">
-        <v>-16.48721984000002</v>
+        <v>-17.95032896000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1261023397915838</v>
+        <v>0.128014300262812</v>
       </c>
       <c r="T59">
-        <v>1.609552794158697</v>
+        <v>1.647875479733904</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05732805013371533</v>
+        <v>0.05633963547623747</v>
       </c>
       <c r="W59">
-        <v>0.18928852753315</v>
+        <v>0.1894870011963715</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5732805013371534</v>
+        <v>0.5633963547623747</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1636684668042765</v>
+        <v>0.1652184668042765</v>
       </c>
       <c r="C60">
-        <v>-63.11489670607591</v>
+        <v>-74.06728757684789</v>
       </c>
       <c r="D60">
-        <v>244.3531032939241</v>
+        <v>241.4967124231521</v>
       </c>
       <c r="E60">
-        <v>185.168</v>
+        <v>193.264</v>
       </c>
       <c r="F60">
-        <v>469.568</v>
+        <v>477.664</v>
       </c>
       <c r="G60">
         <v>162.1</v>
@@ -6335,37 +6335,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M60">
-        <v>94.2892544</v>
+        <v>95.9149312</v>
       </c>
       <c r="N60">
-        <v>-41.16703217777779</v>
+        <v>-42.79270897777779</v>
       </c>
       <c r="O60">
-        <v>-4.116703217777779</v>
+        <v>-4.279270897777779</v>
       </c>
       <c r="P60">
-        <v>-37.05032896000002</v>
+        <v>-38.51343808000001</v>
       </c>
       <c r="Q60">
-        <v>-17.95032896000001</v>
+        <v>-19.41343808000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1280143002628119</v>
+        <v>0.1300195270984903</v>
       </c>
       <c r="T60">
-        <v>1.647875479733903</v>
+        <v>1.688067564605462</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05633963547623749</v>
+        <v>0.05538472640036906</v>
       </c>
       <c r="W60">
-        <v>0.1894870011963715</v>
+        <v>0.1896787469388059</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5633963547623748</v>
+        <v>0.5538472640036906</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1652184668042765</v>
+        <v>0.1667684668042765</v>
       </c>
       <c r="C61">
-        <v>-74.06728757684789</v>
+        <v>-84.9536699083103</v>
       </c>
       <c r="D61">
-        <v>241.4967124231521</v>
+        <v>238.7063300916897</v>
       </c>
       <c r="E61">
-        <v>193.264</v>
+        <v>201.36</v>
       </c>
       <c r="F61">
-        <v>477.664</v>
+        <v>485.76</v>
       </c>
       <c r="G61">
         <v>162.1</v>
@@ -6417,37 +6417,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M61">
-        <v>95.9149312</v>
+        <v>97.54060800000001</v>
       </c>
       <c r="N61">
-        <v>-42.79270897777779</v>
+        <v>-44.41838577777779</v>
       </c>
       <c r="O61">
-        <v>-4.279270897777779</v>
+        <v>-4.441838577777779</v>
       </c>
       <c r="P61">
-        <v>-38.51343808000001</v>
+        <v>-39.97654720000001</v>
       </c>
       <c r="Q61">
-        <v>-19.41343808000001</v>
+        <v>-20.87654720000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1300195270984903</v>
+        <v>0.1321250152759525</v>
       </c>
       <c r="T61">
-        <v>1.688067564605462</v>
+        <v>1.730269253720598</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05538472640036906</v>
+        <v>0.05446164762702957</v>
       </c>
       <c r="W61">
-        <v>0.1896787469388059</v>
+        <v>0.1898641011564925</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5538472640036906</v>
+        <v>0.5446164762702956</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1667684668042765</v>
+        <v>0.1683184668042765</v>
       </c>
       <c r="C62">
-        <v>-84.9536699083103</v>
+        <v>-95.7763056586154</v>
       </c>
       <c r="D62">
-        <v>238.7063300916897</v>
+        <v>235.9796943413846</v>
       </c>
       <c r="E62">
-        <v>201.36</v>
+        <v>209.456</v>
       </c>
       <c r="F62">
-        <v>485.76</v>
+        <v>493.856</v>
       </c>
       <c r="G62">
         <v>162.1</v>
@@ -6499,37 +6499,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M62">
-        <v>97.54060800000001</v>
+        <v>99.1662848</v>
       </c>
       <c r="N62">
-        <v>-44.41838577777779</v>
+        <v>-46.04406257777779</v>
       </c>
       <c r="O62">
-        <v>-4.441838577777779</v>
+        <v>-4.604406257777779</v>
       </c>
       <c r="P62">
-        <v>-39.97654720000001</v>
+        <v>-41.43965632000001</v>
       </c>
       <c r="Q62">
-        <v>-20.87654720000001</v>
+        <v>-22.33965632000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1321250152759525</v>
+        <v>0.1343384772061052</v>
       </c>
       <c r="T62">
-        <v>1.730269253720598</v>
+        <v>1.774635132021127</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05446164762702957</v>
+        <v>0.0535688337315045</v>
       </c>
       <c r="W62">
-        <v>0.1898641011564925</v>
+        <v>0.1900433781867139</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5446164762702956</v>
+        <v>0.5356883373150449</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1683184668042765</v>
+        <v>0.1698684668042765</v>
       </c>
       <c r="C63">
-        <v>-95.7763056586154</v>
+        <v>-106.5373546037473</v>
       </c>
       <c r="D63">
-        <v>235.9796943413846</v>
+        <v>233.3146453962527</v>
       </c>
       <c r="E63">
-        <v>209.456</v>
+        <v>217.552</v>
       </c>
       <c r="F63">
-        <v>493.856</v>
+        <v>501.952</v>
       </c>
       <c r="G63">
         <v>162.1</v>
@@ -6581,37 +6581,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M63">
-        <v>99.1662848</v>
+        <v>100.7919616</v>
       </c>
       <c r="N63">
-        <v>-46.04406257777779</v>
+        <v>-47.66973937777779</v>
       </c>
       <c r="O63">
-        <v>-4.604406257777779</v>
+        <v>-4.76697393777778</v>
       </c>
       <c r="P63">
-        <v>-41.43965632000001</v>
+        <v>-42.90276544000002</v>
       </c>
       <c r="Q63">
-        <v>-22.33965632000001</v>
+        <v>-23.80276544000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1343384772061052</v>
+        <v>0.1366684371325816</v>
       </c>
       <c r="T63">
-        <v>1.774635132021127</v>
+        <v>1.821336056547999</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.0535688337315045</v>
+        <v>0.05270482028422216</v>
       </c>
       <c r="W63">
-        <v>0.1900433781867139</v>
+        <v>0.1902168720869282</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5356883373150449</v>
+        <v>0.5270482028422216</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1698684668042765</v>
+        <v>0.1714184668042765</v>
       </c>
       <c r="C64">
-        <v>-106.5373546037473</v>
+        <v>-117.2388800430846</v>
       </c>
       <c r="D64">
-        <v>233.3146453962527</v>
+        <v>230.7091199569154</v>
       </c>
       <c r="E64">
-        <v>217.552</v>
+        <v>225.648</v>
       </c>
       <c r="F64">
-        <v>501.952</v>
+        <v>510.048</v>
       </c>
       <c r="G64">
         <v>162.1</v>
@@ -6663,37 +6663,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M64">
-        <v>100.7919616</v>
+        <v>102.4176384</v>
       </c>
       <c r="N64">
-        <v>-47.66973937777779</v>
+        <v>-49.29541617777779</v>
       </c>
       <c r="O64">
-        <v>-4.76697393777778</v>
+        <v>-4.92954161777778</v>
       </c>
       <c r="P64">
-        <v>-42.90276544000002</v>
+        <v>-44.36587456000001</v>
       </c>
       <c r="Q64">
-        <v>-23.80276544000002</v>
+        <v>-25.26587456000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1366684371325816</v>
+        <v>0.1391243408388676</v>
       </c>
       <c r="T64">
-        <v>1.821336056547999</v>
+        <v>1.87056135537362</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05270482028422216</v>
+        <v>0.05186823583526626</v>
       </c>
       <c r="W64">
-        <v>0.1902168720869282</v>
+        <v>0.1903848582442786</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5270482028422216</v>
+        <v>0.5186823583526625</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1714184668042765</v>
+        <v>0.1729684668042765</v>
       </c>
       <c r="C65">
-        <v>-117.2388800430846</v>
+        <v>-127.8828541268849</v>
       </c>
       <c r="D65">
-        <v>230.7091199569154</v>
+        <v>228.1611458731151</v>
       </c>
       <c r="E65">
-        <v>225.648</v>
+        <v>233.744</v>
       </c>
       <c r="F65">
-        <v>510.048</v>
+        <v>518.144</v>
       </c>
       <c r="G65">
         <v>162.1</v>
@@ -6745,37 +6745,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M65">
-        <v>102.4176384</v>
+        <v>104.0433152</v>
       </c>
       <c r="N65">
-        <v>-49.29541617777779</v>
+        <v>-50.9210929777778</v>
       </c>
       <c r="O65">
-        <v>-4.92954161777778</v>
+        <v>-5.09210929777778</v>
       </c>
       <c r="P65">
-        <v>-44.36587456000001</v>
+        <v>-45.82898368000001</v>
       </c>
       <c r="Q65">
-        <v>-25.26587456000001</v>
+        <v>-26.72898368000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1391243408388676</v>
+        <v>0.1417166836399473</v>
       </c>
       <c r="T65">
-        <v>1.87056135537362</v>
+        <v>1.922521393022887</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05186823583526626</v>
+        <v>0.05105779465034022</v>
       </c>
       <c r="W65">
-        <v>0.1903848582442786</v>
+        <v>0.1905475948342117</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5186823583526625</v>
+        <v>0.5105779465034022</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1729684668042765</v>
+        <v>0.1745184668042765</v>
       </c>
       <c r="C66">
-        <v>-127.8828541268849</v>
+        <v>-138.4711628346038</v>
       </c>
       <c r="D66">
-        <v>228.1611458731151</v>
+        <v>225.6688371653962</v>
       </c>
       <c r="E66">
-        <v>233.744</v>
+        <v>241.84</v>
       </c>
       <c r="F66">
-        <v>518.144</v>
+        <v>526.24</v>
       </c>
       <c r="G66">
         <v>162.1</v>
@@ -6827,37 +6827,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M66">
-        <v>104.0433152</v>
+        <v>105.668992</v>
       </c>
       <c r="N66">
-        <v>-50.9210929777778</v>
+        <v>-52.54676977777779</v>
       </c>
       <c r="O66">
-        <v>-5.09210929777778</v>
+        <v>-5.25467697777778</v>
       </c>
       <c r="P66">
-        <v>-45.82898368000001</v>
+        <v>-47.29209280000001</v>
       </c>
       <c r="Q66">
-        <v>-26.72898368000001</v>
+        <v>-28.19209280000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1417166836399473</v>
+        <v>0.1444571603153743</v>
       </c>
       <c r="T66">
-        <v>1.922521393022887</v>
+        <v>1.977450575680684</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05105779465034022</v>
+        <v>0.05027229011725806</v>
       </c>
       <c r="W66">
-        <v>0.1905475948342117</v>
+        <v>0.1907053241444546</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5105779465034022</v>
+        <v>0.5027229011725807</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1745184668042765</v>
+        <v>0.1993416044093541</v>
       </c>
       <c r="C67">
-        <v>-138.4711628346038</v>
+        <v>-180.1673440346157</v>
       </c>
       <c r="D67">
-        <v>225.6688371653962</v>
+        <v>192.0686559653843</v>
       </c>
       <c r="E67">
-        <v>241.84</v>
+        <v>249.936</v>
       </c>
       <c r="F67">
-        <v>526.24</v>
+        <v>534.336</v>
       </c>
       <c r="G67">
         <v>162.1</v>
@@ -6909,45 +6909,45 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M67">
-        <v>105.668992</v>
+        <v>125.9964288</v>
       </c>
       <c r="N67">
-        <v>-52.54676977777779</v>
+        <v>-72.87420657777778</v>
       </c>
       <c r="O67">
-        <v>-5.25467697777778</v>
+        <v>-7.287420657777779</v>
       </c>
       <c r="P67">
-        <v>-47.29209280000001</v>
+        <v>-65.58678592000001</v>
       </c>
       <c r="Q67">
-        <v>-28.19209280000001</v>
+        <v>-46.48678592000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1444571603153743</v>
+        <v>0.1478680697513488</v>
       </c>
       <c r="T67">
-        <v>1.977450575680684</v>
+        <v>2.045817684628491</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05027229011725806</v>
+        <v>0.04216168880988333</v>
       </c>
       <c r="W67">
-        <v>0.1907053241444546</v>
+        <v>0.2258582737786295</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5027229011725807</v>
+        <v>0.4216168880988334</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1993416044093541</v>
+        <v>0.2012416044093541</v>
       </c>
       <c r="C68">
-        <v>-180.1673440346157</v>
+        <v>-190.4275672766237</v>
       </c>
       <c r="D68">
-        <v>192.0686559653843</v>
+        <v>189.9044327233763</v>
       </c>
       <c r="E68">
-        <v>249.936</v>
+        <v>258.032</v>
       </c>
       <c r="F68">
-        <v>534.336</v>
+        <v>542.432</v>
       </c>
       <c r="G68">
         <v>162.1</v>
@@ -6991,37 +6991,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M68">
-        <v>125.9964288</v>
+        <v>127.9054656</v>
       </c>
       <c r="N68">
-        <v>-72.87420657777778</v>
+        <v>-74.78324337777781</v>
       </c>
       <c r="O68">
-        <v>-7.287420657777779</v>
+        <v>-7.478324337777781</v>
       </c>
       <c r="P68">
-        <v>-65.58678592000001</v>
+        <v>-67.30491904000003</v>
       </c>
       <c r="Q68">
-        <v>-46.48678592000001</v>
+        <v>-48.20491904000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1478680697513488</v>
+        <v>0.1509610415619957</v>
       </c>
       <c r="T68">
-        <v>2.045817684628491</v>
+        <v>2.107812159920263</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04216168880988333</v>
+        <v>0.04153240987242238</v>
       </c>
       <c r="W68">
-        <v>0.2258582737786295</v>
+        <v>0.2260066577520828</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4216168880988334</v>
+        <v>0.4153240987242237</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2012416044093541</v>
+        <v>0.2031416044093541</v>
       </c>
       <c r="C69">
-        <v>-190.4275672766237</v>
+        <v>-200.6395611739362</v>
       </c>
       <c r="D69">
-        <v>189.9044327233763</v>
+        <v>187.7884388260638</v>
       </c>
       <c r="E69">
-        <v>258.032</v>
+        <v>266.128</v>
       </c>
       <c r="F69">
-        <v>542.432</v>
+        <v>550.528</v>
       </c>
       <c r="G69">
         <v>162.1</v>
@@ -7073,37 +7073,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M69">
-        <v>127.9054656</v>
+        <v>129.8145024</v>
       </c>
       <c r="N69">
-        <v>-74.78324337777781</v>
+        <v>-76.6922801777778</v>
       </c>
       <c r="O69">
-        <v>-7.478324337777781</v>
+        <v>-7.669228017777781</v>
       </c>
       <c r="P69">
-        <v>-67.30491904000003</v>
+        <v>-69.02305216000002</v>
       </c>
       <c r="Q69">
-        <v>-48.20491904000003</v>
+        <v>-49.92305216000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1509610415619957</v>
+        <v>0.1542473241108081</v>
       </c>
       <c r="T69">
-        <v>2.107812159920263</v>
+        <v>2.173681289917771</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04153240987242238</v>
+        <v>0.0409216391390044</v>
       </c>
       <c r="W69">
-        <v>0.2260066577520828</v>
+        <v>0.2261506774910228</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4153240987242237</v>
+        <v>0.409216391390044</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2031416044093541</v>
+        <v>0.2050416044093541</v>
       </c>
       <c r="C70">
-        <v>-200.6395611739362</v>
+        <v>-210.8049201350362</v>
       </c>
       <c r="D70">
-        <v>187.7884388260638</v>
+        <v>185.7190798649638</v>
       </c>
       <c r="E70">
-        <v>266.128</v>
+        <v>274.224</v>
       </c>
       <c r="F70">
-        <v>550.528</v>
+        <v>558.624</v>
       </c>
       <c r="G70">
         <v>162.1</v>
@@ -7155,37 +7155,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M70">
-        <v>129.8145024</v>
+        <v>131.7235392</v>
       </c>
       <c r="N70">
-        <v>-76.6922801777778</v>
+        <v>-78.6013169777778</v>
       </c>
       <c r="O70">
-        <v>-7.669228017777781</v>
+        <v>-7.86013169777778</v>
       </c>
       <c r="P70">
-        <v>-69.02305216000002</v>
+        <v>-70.74118528000002</v>
       </c>
       <c r="Q70">
-        <v>-49.92305216000002</v>
+        <v>-51.64118528000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1542473241108081</v>
+        <v>0.1577456248885761</v>
       </c>
       <c r="T70">
-        <v>2.173681289917771</v>
+        <v>2.243800041205442</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0409216391390044</v>
+        <v>0.04032857190510579</v>
       </c>
       <c r="W70">
-        <v>0.2261506774910228</v>
+        <v>0.2262905227447761</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.409216391390044</v>
+        <v>0.4032857190510578</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2050416044093541</v>
+        <v>0.2069416044093541</v>
       </c>
       <c r="C71">
-        <v>-210.8049201350362</v>
+        <v>-220.9251690552553</v>
       </c>
       <c r="D71">
-        <v>185.7190798649638</v>
+        <v>183.6948309447447</v>
       </c>
       <c r="E71">
-        <v>274.224</v>
+        <v>282.3200000000001</v>
       </c>
       <c r="F71">
-        <v>558.624</v>
+        <v>566.72</v>
       </c>
       <c r="G71">
         <v>162.1</v>
@@ -7237,37 +7237,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M71">
-        <v>131.7235392</v>
+        <v>133.632576</v>
       </c>
       <c r="N71">
-        <v>-78.6013169777778</v>
+        <v>-80.51035377777779</v>
       </c>
       <c r="O71">
-        <v>-7.86013169777778</v>
+        <v>-8.051035377777779</v>
       </c>
       <c r="P71">
-        <v>-70.74118528000002</v>
+        <v>-72.45931840000002</v>
       </c>
       <c r="Q71">
-        <v>-51.64118528000002</v>
+        <v>-53.35931840000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1577456248885761</v>
+        <v>0.1614771457181953</v>
       </c>
       <c r="T71">
-        <v>2.243800041205442</v>
+        <v>2.31859337591229</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04032857190510579</v>
+        <v>0.03975244944931857</v>
       </c>
       <c r="W71">
-        <v>0.2262905227447761</v>
+        <v>0.2264263724198507</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4032857190510578</v>
+        <v>0.3975244944931856</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2069416044093541</v>
+        <v>0.2088416044093541</v>
       </c>
       <c r="C72">
-        <v>-220.9251690552553</v>
+        <v>-231.0017670642272</v>
       </c>
       <c r="D72">
-        <v>183.6948309447447</v>
+        <v>181.7142329357729</v>
       </c>
       <c r="E72">
-        <v>282.3200000000001</v>
+        <v>290.4160000000001</v>
       </c>
       <c r="F72">
-        <v>566.72</v>
+        <v>574.816</v>
       </c>
       <c r="G72">
         <v>162.1</v>
@@ -7319,37 +7319,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M72">
-        <v>133.632576</v>
+        <v>135.5416128</v>
       </c>
       <c r="N72">
-        <v>-80.51035377777779</v>
+        <v>-82.41939057777782</v>
       </c>
       <c r="O72">
-        <v>-8.051035377777779</v>
+        <v>-8.241939057777783</v>
       </c>
       <c r="P72">
-        <v>-72.45931840000002</v>
+        <v>-74.17745152000003</v>
       </c>
       <c r="Q72">
-        <v>-53.35931840000001</v>
+        <v>-55.07745152000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1614771457181953</v>
+        <v>0.1654660128119262</v>
       </c>
       <c r="T72">
-        <v>2.31859337591229</v>
+        <v>2.398544871633403</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03975244944931857</v>
+        <v>0.03919255579510281</v>
       </c>
       <c r="W72">
-        <v>0.2264263724198507</v>
+        <v>0.2265583953435148</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3975244944931856</v>
+        <v>0.391925557951028</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2088416044093541</v>
+        <v>0.2107416044093541</v>
       </c>
       <c r="C73">
-        <v>-231.0017670642274</v>
+        <v>-241.0361110334994</v>
       </c>
       <c r="D73">
-        <v>181.7142329357727</v>
+        <v>179.7758889665006</v>
       </c>
       <c r="E73">
-        <v>290.4160000000001</v>
+        <v>298.5120000000001</v>
       </c>
       <c r="F73">
-        <v>574.816</v>
+        <v>582.912</v>
       </c>
       <c r="G73">
         <v>162.1</v>
@@ -7401,37 +7401,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M73">
-        <v>135.5416128</v>
+        <v>137.4506496</v>
       </c>
       <c r="N73">
-        <v>-82.41939057777782</v>
+        <v>-84.32842737777781</v>
       </c>
       <c r="O73">
-        <v>-8.241939057777783</v>
+        <v>-8.432842737777781</v>
       </c>
       <c r="P73">
-        <v>-74.17745152000003</v>
+        <v>-75.89558464000004</v>
       </c>
       <c r="Q73">
-        <v>-55.07745152000003</v>
+        <v>-56.79558464000004</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1654660128119262</v>
+        <v>0.1697397989837807</v>
       </c>
       <c r="T73">
-        <v>2.398544871633403</v>
+        <v>2.484207188477453</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03919255579510281</v>
+        <v>0.03864821474239305</v>
       </c>
       <c r="W73">
-        <v>0.2265583953435148</v>
+        <v>0.2266867509637437</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.391925557951028</v>
+        <v>0.3864821474239304</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2107416044093541</v>
+        <v>0.2126416044093541</v>
       </c>
       <c r="C74">
-        <v>-241.0361110334994</v>
+        <v>-251.0295388620179</v>
       </c>
       <c r="D74">
-        <v>179.7758889665006</v>
+        <v>177.8784611379821</v>
       </c>
       <c r="E74">
-        <v>298.5120000000001</v>
+        <v>306.6080000000001</v>
       </c>
       <c r="F74">
-        <v>582.912</v>
+        <v>591.008</v>
       </c>
       <c r="G74">
         <v>162.1</v>
@@ -7483,37 +7483,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M74">
-        <v>137.4506496</v>
+        <v>139.3596864</v>
       </c>
       <c r="N74">
-        <v>-84.32842737777781</v>
+        <v>-86.23746417777781</v>
       </c>
       <c r="O74">
-        <v>-8.432842737777781</v>
+        <v>-8.623746417777781</v>
       </c>
       <c r="P74">
-        <v>-75.89558464000004</v>
+        <v>-77.61371776000003</v>
       </c>
       <c r="Q74">
-        <v>-56.79558464000004</v>
+        <v>-58.51371776000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1697397989837807</v>
+        <v>0.1743301619091059</v>
       </c>
       <c r="T74">
-        <v>2.484207188477453</v>
+        <v>2.576214862124766</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03864821474239305</v>
+        <v>0.03811878714318218</v>
       </c>
       <c r="W74">
-        <v>0.2266867509637437</v>
+        <v>0.2268115899916376</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3864821474239304</v>
+        <v>0.3811878714318218</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2126416044093541</v>
+        <v>0.214541604409354</v>
       </c>
       <c r="C75">
-        <v>-251.0295388620179</v>
+        <v>-260.9833325557286</v>
       </c>
       <c r="D75">
-        <v>177.8784611379821</v>
+        <v>176.0206674442715</v>
       </c>
       <c r="E75">
-        <v>306.6080000000001</v>
+        <v>314.7040000000001</v>
       </c>
       <c r="F75">
-        <v>591.008</v>
+        <v>599.104</v>
       </c>
       <c r="G75">
         <v>162.1</v>
@@ -7565,37 +7565,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M75">
-        <v>139.3596864</v>
+        <v>141.2687232</v>
       </c>
       <c r="N75">
-        <v>-86.23746417777781</v>
+        <v>-88.14650097777781</v>
       </c>
       <c r="O75">
-        <v>-8.623746417777781</v>
+        <v>-8.814650097777781</v>
       </c>
       <c r="P75">
-        <v>-77.61371776000003</v>
+        <v>-79.33185088000002</v>
       </c>
       <c r="Q75">
-        <v>-58.51371776000003</v>
+        <v>-60.23185088000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1743301619091059</v>
+        <v>0.1792736296748407</v>
       </c>
       <c r="T75">
-        <v>2.576214862124766</v>
+        <v>2.675300049129564</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03811878714318218</v>
+        <v>0.03760366839800405</v>
       </c>
       <c r="W75">
-        <v>0.2268115899916376</v>
+        <v>0.2269330549917506</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3811878714318218</v>
+        <v>0.3760366839800404</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.214541604409354</v>
+        <v>0.2164416044093541</v>
       </c>
       <c r="C76">
-        <v>-260.9833325557286</v>
+        <v>-270.8987211161883</v>
       </c>
       <c r="D76">
-        <v>176.0206674442715</v>
+        <v>174.2012788838117</v>
       </c>
       <c r="E76">
-        <v>314.7040000000001</v>
+        <v>322.8000000000001</v>
       </c>
       <c r="F76">
-        <v>599.104</v>
+        <v>607.2</v>
       </c>
       <c r="G76">
         <v>162.1</v>
@@ -7647,37 +7647,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M76">
-        <v>141.2687232</v>
+        <v>143.17776</v>
       </c>
       <c r="N76">
-        <v>-88.14650097777781</v>
+        <v>-90.0555377777778</v>
       </c>
       <c r="O76">
-        <v>-8.814650097777781</v>
+        <v>-9.005553777777781</v>
       </c>
       <c r="P76">
-        <v>-79.33185088000002</v>
+        <v>-81.04998400000002</v>
       </c>
       <c r="Q76">
-        <v>-60.23185088000002</v>
+        <v>-61.94998400000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1792736296748407</v>
+        <v>0.1846125748618344</v>
       </c>
       <c r="T76">
-        <v>2.675300049129564</v>
+        <v>2.782312051094747</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03760366839800405</v>
+        <v>0.03710228615269733</v>
       </c>
       <c r="W76">
-        <v>0.2269330549917506</v>
+        <v>0.227051280925194</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3760366839800404</v>
+        <v>0.3710228615269732</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2164416044093541</v>
+        <v>0.2183416044093541</v>
       </c>
       <c r="C77">
-        <v>-270.8987211161883</v>
+        <v>-280.7768832518676</v>
       </c>
       <c r="D77">
-        <v>174.2012788838117</v>
+        <v>172.4191167481324</v>
       </c>
       <c r="E77">
-        <v>322.8000000000001</v>
+        <v>330.8960000000001</v>
       </c>
       <c r="F77">
-        <v>607.2</v>
+        <v>615.296</v>
       </c>
       <c r="G77">
         <v>162.1</v>
@@ -7729,37 +7729,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M77">
-        <v>143.17776</v>
+        <v>145.0867968</v>
       </c>
       <c r="N77">
-        <v>-90.0555377777778</v>
+        <v>-91.96457457777782</v>
       </c>
       <c r="O77">
-        <v>-9.005553777777781</v>
+        <v>-9.196457457777782</v>
       </c>
       <c r="P77">
-        <v>-81.04998400000002</v>
+        <v>-82.76811712000004</v>
       </c>
       <c r="Q77">
-        <v>-61.94998400000002</v>
+        <v>-63.66811712000004</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1846125748618344</v>
+        <v>0.1903964321477441</v>
       </c>
       <c r="T77">
-        <v>2.782312051094747</v>
+        <v>2.898241719890362</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03710228615269733</v>
+        <v>0.03661409817700394</v>
       </c>
       <c r="W77">
-        <v>0.227051280925194</v>
+        <v>0.2271663956498625</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3710228615269732</v>
+        <v>0.3661409817700393</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2183416044093541</v>
+        <v>0.2202416044093541</v>
       </c>
       <c r="C78">
-        <v>-280.7768832518676</v>
+        <v>-290.6189499247072</v>
       </c>
       <c r="D78">
-        <v>172.4191167481324</v>
+        <v>170.6730500752928</v>
       </c>
       <c r="E78">
-        <v>330.8960000000001</v>
+        <v>338.9920000000001</v>
       </c>
       <c r="F78">
-        <v>615.296</v>
+        <v>623.3920000000001</v>
       </c>
       <c r="G78">
         <v>162.1</v>
@@ -7811,37 +7811,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M78">
-        <v>145.0867968</v>
+        <v>146.9958336</v>
       </c>
       <c r="N78">
-        <v>-91.96457457777782</v>
+        <v>-93.87361137777782</v>
       </c>
       <c r="O78">
-        <v>-9.196457457777782</v>
+        <v>-9.387361137777782</v>
       </c>
       <c r="P78">
-        <v>-82.76811712000004</v>
+        <v>-84.48625024000003</v>
       </c>
       <c r="Q78">
-        <v>-63.66811712000004</v>
+        <v>-65.38625024000004</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1903964321477441</v>
+        <v>0.1966832335454721</v>
       </c>
       <c r="T78">
-        <v>2.898241719890362</v>
+        <v>3.024252229450812</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03661409817700394</v>
+        <v>0.03613859040847141</v>
       </c>
       <c r="W78">
-        <v>0.2271663956498625</v>
+        <v>0.2272785203816824</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3661409817700393</v>
+        <v>0.3613859040847142</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2202416044093541</v>
+        <v>0.2221416044093541</v>
       </c>
       <c r="C79">
-        <v>-290.6189499247072</v>
+        <v>-300.4260067434976</v>
       </c>
       <c r="D79">
-        <v>170.6730500752928</v>
+        <v>168.9619932565024</v>
       </c>
       <c r="E79">
-        <v>338.9920000000001</v>
+        <v>347.0880000000001</v>
       </c>
       <c r="F79">
-        <v>623.3920000000001</v>
+        <v>631.4880000000001</v>
       </c>
       <c r="G79">
         <v>162.1</v>
@@ -7893,37 +7893,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M79">
-        <v>146.9958336</v>
+        <v>148.9048704</v>
       </c>
       <c r="N79">
-        <v>-93.87361137777782</v>
+        <v>-95.78264817777782</v>
       </c>
       <c r="O79">
-        <v>-9.387361137777782</v>
+        <v>-9.578264817777782</v>
       </c>
       <c r="P79">
-        <v>-84.48625024000003</v>
+        <v>-86.20438336000004</v>
       </c>
       <c r="Q79">
-        <v>-65.38625024000004</v>
+        <v>-67.10438336000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1966832335454721</v>
+        <v>0.2035415623429936</v>
       </c>
       <c r="T79">
-        <v>3.024252229450812</v>
+        <v>3.161718239880395</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03613859040847141</v>
+        <v>0.03567527514682435</v>
       </c>
       <c r="W79">
-        <v>0.2272785203816824</v>
+        <v>0.2273877701203788</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3613859040847142</v>
+        <v>0.3567527514682435</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2221416044093541</v>
+        <v>0.2240416044093541</v>
       </c>
       <c r="C80">
-        <v>-300.4260067434976</v>
+        <v>-310.1990962147189</v>
       </c>
       <c r="D80">
-        <v>168.9619932565024</v>
+        <v>167.2849037852812</v>
       </c>
       <c r="E80">
-        <v>347.0880000000001</v>
+        <v>355.1840000000001</v>
       </c>
       <c r="F80">
-        <v>631.4880000000001</v>
+        <v>639.5840000000001</v>
       </c>
       <c r="G80">
         <v>162.1</v>
@@ -7975,37 +7975,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M80">
-        <v>148.9048704</v>
+        <v>150.8139072</v>
       </c>
       <c r="N80">
-        <v>-95.78264817777782</v>
+        <v>-97.69168497777781</v>
       </c>
       <c r="O80">
-        <v>-9.578264817777782</v>
+        <v>-9.769168497777782</v>
       </c>
       <c r="P80">
-        <v>-86.20438336000004</v>
+        <v>-87.92251648000003</v>
       </c>
       <c r="Q80">
-        <v>-67.10438336000004</v>
+        <v>-68.82251648000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2035415623429936</v>
+        <v>0.2110530653117076</v>
       </c>
       <c r="T80">
-        <v>3.161718239880395</v>
+        <v>3.31227625130327</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03567527514682435</v>
+        <v>0.03522368938547214</v>
       </c>
       <c r="W80">
-        <v>0.2273877701203788</v>
+        <v>0.2274942540429057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3567527514682435</v>
+        <v>0.3522368938547213</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2240416044093541</v>
+        <v>0.2259416044093541</v>
       </c>
       <c r="C81">
-        <v>-310.1990962147189</v>
+        <v>-319.9392198606497</v>
       </c>
       <c r="D81">
-        <v>167.2849037852812</v>
+        <v>165.6407801393504</v>
       </c>
       <c r="E81">
-        <v>355.1840000000001</v>
+        <v>363.2800000000001</v>
       </c>
       <c r="F81">
-        <v>639.5840000000001</v>
+        <v>647.6800000000001</v>
       </c>
       <c r="G81">
         <v>162.1</v>
@@ -8057,37 +8057,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M81">
-        <v>150.8139072</v>
+        <v>152.722944</v>
       </c>
       <c r="N81">
-        <v>-97.69168497777781</v>
+        <v>-99.60072177777781</v>
       </c>
       <c r="O81">
-        <v>-9.769168497777782</v>
+        <v>-9.960072177777782</v>
       </c>
       <c r="P81">
-        <v>-87.92251648000003</v>
+        <v>-89.64064960000002</v>
       </c>
       <c r="Q81">
-        <v>-68.82251648000002</v>
+        <v>-70.54064960000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2110530653117076</v>
+        <v>0.219315718577293</v>
       </c>
       <c r="T81">
-        <v>3.31227625130327</v>
+        <v>3.477890063868434</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03522368938547214</v>
+        <v>0.03478339326815374</v>
       </c>
       <c r="W81">
-        <v>0.2274942540429057</v>
+        <v>0.2275980758673694</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3522368938547213</v>
+        <v>0.3478339326815374</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2259416044093541</v>
+        <v>0.2278416044093541</v>
       </c>
       <c r="C82">
-        <v>-319.9392198606497</v>
+        <v>-329.6473402137867</v>
       </c>
       <c r="D82">
-        <v>165.6407801393504</v>
+        <v>164.0286597862134</v>
       </c>
       <c r="E82">
-        <v>363.2800000000001</v>
+        <v>371.3760000000001</v>
       </c>
       <c r="F82">
-        <v>647.6800000000001</v>
+        <v>655.7760000000001</v>
       </c>
       <c r="G82">
         <v>162.1</v>
@@ -8139,37 +8139,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M82">
-        <v>152.722944</v>
+        <v>154.6319808</v>
       </c>
       <c r="N82">
-        <v>-99.60072177777781</v>
+        <v>-101.5097585777778</v>
       </c>
       <c r="O82">
-        <v>-9.960072177777782</v>
+        <v>-10.15097585777778</v>
       </c>
       <c r="P82">
-        <v>-89.64064960000002</v>
+        <v>-91.35878272000002</v>
       </c>
       <c r="Q82">
-        <v>-70.54064960000002</v>
+        <v>-72.25878272000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.219315718577293</v>
+        <v>0.2284481248182031</v>
       </c>
       <c r="T82">
-        <v>3.477890063868434</v>
+        <v>3.660936909335194</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03478339326815374</v>
+        <v>0.03435396865990493</v>
       </c>
       <c r="W82">
-        <v>0.2275980758673694</v>
+        <v>0.2276993341899944</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3478339326815374</v>
+        <v>0.3435396865990492</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2278416044093541</v>
+        <v>0.2297416044093541</v>
       </c>
       <c r="C83">
-        <v>-329.6473402137867</v>
+        <v>-339.3243826959233</v>
       </c>
       <c r="D83">
-        <v>164.0286597862134</v>
+        <v>162.4476173040768</v>
       </c>
       <c r="E83">
-        <v>371.3760000000001</v>
+        <v>379.4720000000001</v>
       </c>
       <c r="F83">
-        <v>655.7760000000001</v>
+        <v>663.8720000000001</v>
       </c>
       <c r="G83">
         <v>162.1</v>
@@ -8221,37 +8221,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M83">
-        <v>154.6319808</v>
+        <v>156.5410176</v>
       </c>
       <c r="N83">
-        <v>-101.5097585777778</v>
+        <v>-103.4187953777778</v>
       </c>
       <c r="O83">
-        <v>-10.15097585777778</v>
+        <v>-10.34187953777778</v>
       </c>
       <c r="P83">
-        <v>-91.35878272000002</v>
+        <v>-93.07691584000004</v>
       </c>
       <c r="Q83">
-        <v>-72.25878272000003</v>
+        <v>-73.97691584000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2284481248182031</v>
+        <v>0.2385952428636589</v>
       </c>
       <c r="T83">
-        <v>3.660936909335194</v>
+        <v>3.86432229318715</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03435396865990493</v>
+        <v>0.03393501782258902</v>
       </c>
       <c r="W83">
-        <v>0.2276993341899944</v>
+        <v>0.2277981227974335</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3435396865990492</v>
+        <v>0.3393501782258901</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2297416044093541</v>
+        <v>0.2316416044093541</v>
       </c>
       <c r="C84">
-        <v>-339.3243826959233</v>
+        <v>-348.9712373895896</v>
       </c>
       <c r="D84">
-        <v>162.4476173040768</v>
+        <v>160.8967626104105</v>
       </c>
       <c r="E84">
-        <v>379.4720000000001</v>
+        <v>387.5680000000001</v>
       </c>
       <c r="F84">
-        <v>663.8720000000001</v>
+        <v>671.9680000000001</v>
       </c>
       <c r="G84">
         <v>162.1</v>
@@ -8303,37 +8303,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M84">
-        <v>156.5410176</v>
+        <v>158.4500544</v>
       </c>
       <c r="N84">
-        <v>-103.4187953777778</v>
+        <v>-105.3278321777778</v>
       </c>
       <c r="O84">
-        <v>-10.34187953777778</v>
+        <v>-10.53278321777778</v>
       </c>
       <c r="P84">
-        <v>-93.07691584000004</v>
+        <v>-94.79504896000003</v>
       </c>
       <c r="Q84">
-        <v>-73.97691584000003</v>
+        <v>-75.69504896000004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2385952428636589</v>
+        <v>0.2499361395026977</v>
       </c>
       <c r="T84">
-        <v>3.86432229318715</v>
+        <v>4.091635369256982</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03393501782258902</v>
+        <v>0.03352616218617228</v>
       </c>
       <c r="W84">
-        <v>0.2277981227974335</v>
+        <v>0.2278945309565006</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3393501782258901</v>
+        <v>0.3352616218617227</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2316416044093541</v>
+        <v>0.2335416044093541</v>
       </c>
       <c r="C85">
-        <v>-348.9712373895896</v>
+        <v>-358.5887607089871</v>
       </c>
       <c r="D85">
-        <v>160.8967626104105</v>
+        <v>159.3752392910129</v>
       </c>
       <c r="E85">
-        <v>387.5680000000001</v>
+        <v>395.6640000000001</v>
       </c>
       <c r="F85">
-        <v>671.9680000000001</v>
+        <v>680.0640000000001</v>
       </c>
       <c r="G85">
         <v>162.1</v>
@@ -8385,37 +8385,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M85">
-        <v>158.4500544</v>
+        <v>160.3590912</v>
       </c>
       <c r="N85">
-        <v>-105.3278321777778</v>
+        <v>-107.2368689777778</v>
       </c>
       <c r="O85">
-        <v>-10.53278321777778</v>
+        <v>-10.72368689777778</v>
       </c>
       <c r="P85">
-        <v>-94.79504896000003</v>
+        <v>-96.51318208000004</v>
       </c>
       <c r="Q85">
-        <v>-75.69504896000004</v>
+        <v>-77.41318208000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2499361395026977</v>
+        <v>0.2626946482216163</v>
       </c>
       <c r="T85">
-        <v>4.091635369256982</v>
+        <v>4.347362579835545</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03352616218617228</v>
+        <v>0.03312704120776547</v>
       </c>
       <c r="W85">
-        <v>0.2278945309565006</v>
+        <v>0.2279886436832089</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3352616218617227</v>
+        <v>0.3312704120776546</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2335416044093541</v>
+        <v>0.2354416044093541</v>
       </c>
       <c r="C86">
-        <v>-358.588760708987</v>
+        <v>-368.1777769769989</v>
       </c>
       <c r="D86">
-        <v>159.3752392910129</v>
+        <v>157.882223023001</v>
       </c>
       <c r="E86">
-        <v>395.664</v>
+        <v>403.76</v>
       </c>
       <c r="F86">
-        <v>680.064</v>
+        <v>688.16</v>
       </c>
       <c r="G86">
         <v>162.1</v>
@@ -8467,37 +8467,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M86">
-        <v>160.3590912</v>
+        <v>162.268128</v>
       </c>
       <c r="N86">
-        <v>-107.2368689777778</v>
+        <v>-109.1459057777778</v>
       </c>
       <c r="O86">
-        <v>-10.72368689777778</v>
+        <v>-10.91459057777778</v>
       </c>
       <c r="P86">
-        <v>-96.51318208000001</v>
+        <v>-98.23131520000001</v>
       </c>
       <c r="Q86">
-        <v>-77.41318208000001</v>
+        <v>-79.13131520000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2626946482216161</v>
+        <v>0.2771542914363906</v>
       </c>
       <c r="T86">
-        <v>4.347362579835542</v>
+        <v>4.637186751824578</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03312704120776547</v>
+        <v>0.03273731131120353</v>
       </c>
       <c r="W86">
-        <v>0.2279886436832089</v>
+        <v>0.2280805419928182</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3312704120776547</v>
+        <v>0.3273731131120352</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2354416044093541</v>
+        <v>0.2373416044093541</v>
       </c>
       <c r="C87">
-        <v>-368.1777769769989</v>
+        <v>-377.7390799143874</v>
       </c>
       <c r="D87">
-        <v>157.882223023001</v>
+        <v>156.4169200856125</v>
       </c>
       <c r="E87">
-        <v>403.76</v>
+        <v>411.856</v>
       </c>
       <c r="F87">
-        <v>688.16</v>
+        <v>696.256</v>
       </c>
       <c r="G87">
         <v>162.1</v>
@@ -8549,37 +8549,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M87">
-        <v>162.268128</v>
+        <v>164.1771648</v>
       </c>
       <c r="N87">
-        <v>-109.1459057777778</v>
+        <v>-111.0549425777778</v>
       </c>
       <c r="O87">
-        <v>-10.91459057777778</v>
+        <v>-11.10549425777778</v>
       </c>
       <c r="P87">
-        <v>-98.23131520000001</v>
+        <v>-99.94944832000003</v>
       </c>
       <c r="Q87">
-        <v>-79.13131520000002</v>
+        <v>-80.84944832000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2771542914363906</v>
+        <v>0.2936795979675614</v>
       </c>
       <c r="T87">
-        <v>4.637186751824578</v>
+        <v>4.968414376954906</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03273731131120353</v>
+        <v>0.03235664490060813</v>
       </c>
       <c r="W87">
-        <v>0.2280805419928182</v>
+        <v>0.2281703031324366</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3273731131120352</v>
+        <v>0.3235664490060812</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2373416044093541</v>
+        <v>0.2392416044093541</v>
       </c>
       <c r="C88">
-        <v>-377.7390799143874</v>
+        <v>-387.2734340468244</v>
       </c>
       <c r="D88">
-        <v>156.4169200856125</v>
+        <v>154.9785659531756</v>
       </c>
       <c r="E88">
-        <v>411.856</v>
+        <v>419.952</v>
       </c>
       <c r="F88">
-        <v>696.256</v>
+        <v>704.352</v>
       </c>
       <c r="G88">
         <v>162.1</v>
@@ -8631,37 +8631,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M88">
-        <v>164.1771648</v>
+        <v>166.0862016</v>
       </c>
       <c r="N88">
-        <v>-111.0549425777778</v>
+        <v>-112.9639793777778</v>
       </c>
       <c r="O88">
-        <v>-11.10549425777778</v>
+        <v>-11.29639793777778</v>
       </c>
       <c r="P88">
-        <v>-99.94944832000003</v>
+        <v>-101.66758144</v>
       </c>
       <c r="Q88">
-        <v>-80.84944832000002</v>
+        <v>-82.56758144000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2936795979675614</v>
+        <v>0.3127472593496815</v>
       </c>
       <c r="T88">
-        <v>4.968414376954906</v>
+        <v>5.350600098259128</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03235664490060813</v>
+        <v>0.03198472944198046</v>
       </c>
       <c r="W88">
-        <v>0.2281703031324366</v>
+        <v>0.228258000797581</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3235664490060812</v>
+        <v>0.3198472944198045</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2392416044093541</v>
+        <v>0.2411416044093541</v>
       </c>
       <c r="C89">
-        <v>-387.2734340468244</v>
+        <v>-396.7815760349977</v>
       </c>
       <c r="D89">
-        <v>154.9785659531756</v>
+        <v>153.5664239650023</v>
       </c>
       <c r="E89">
-        <v>419.952</v>
+        <v>428.048</v>
       </c>
       <c r="F89">
-        <v>704.352</v>
+        <v>712.448</v>
       </c>
       <c r="G89">
         <v>162.1</v>
@@ -8713,37 +8713,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M89">
-        <v>166.0862016</v>
+        <v>167.9952384</v>
       </c>
       <c r="N89">
-        <v>-112.9639793777778</v>
+        <v>-114.8730161777778</v>
       </c>
       <c r="O89">
-        <v>-11.29639793777778</v>
+        <v>-11.48730161777778</v>
       </c>
       <c r="P89">
-        <v>-101.66758144</v>
+        <v>-103.38571456</v>
       </c>
       <c r="Q89">
-        <v>-82.56758144000003</v>
+        <v>-84.28571456000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3127472593496815</v>
+        <v>0.3349928642954882</v>
       </c>
       <c r="T89">
-        <v>5.350600098259128</v>
+        <v>5.796483439780723</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03198472944198046</v>
+        <v>0.0316212666074125</v>
       </c>
       <c r="W89">
-        <v>0.228258000797581</v>
+        <v>0.2283437053339721</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3198472944198045</v>
+        <v>0.3162126660741249</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2411416044093541</v>
+        <v>0.2430416044093541</v>
       </c>
       <c r="C90">
-        <v>-396.7815760349977</v>
+        <v>-406.2642159326566</v>
       </c>
       <c r="D90">
-        <v>153.5664239650023</v>
+        <v>152.1797840673434</v>
       </c>
       <c r="E90">
-        <v>428.048</v>
+        <v>436.144</v>
       </c>
       <c r="F90">
-        <v>712.448</v>
+        <v>720.544</v>
       </c>
       <c r="G90">
         <v>162.1</v>
@@ -8795,37 +8795,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M90">
-        <v>167.9952384</v>
+        <v>169.9042752</v>
       </c>
       <c r="N90">
-        <v>-114.8730161777778</v>
+        <v>-116.7820529777778</v>
       </c>
       <c r="O90">
-        <v>-11.48730161777778</v>
+        <v>-11.67820529777778</v>
       </c>
       <c r="P90">
-        <v>-103.38571456</v>
+        <v>-105.10384768</v>
       </c>
       <c r="Q90">
-        <v>-84.28571456000003</v>
+        <v>-86.00384768000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3349928642954882</v>
+        <v>0.3612831246859872</v>
       </c>
       <c r="T90">
-        <v>5.796483439780723</v>
+        <v>6.323436479760789</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0316212666074125</v>
+        <v>0.03126597147699213</v>
       </c>
       <c r="W90">
-        <v>0.2283437053339721</v>
+        <v>0.2284274839257253</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3162126660741249</v>
+        <v>0.3126597147699213</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2430416044093541</v>
+        <v>0.2449416044093541</v>
       </c>
       <c r="C91">
-        <v>-406.2642159326566</v>
+        <v>-415.7220383771093</v>
       </c>
       <c r="D91">
-        <v>152.1797840673434</v>
+        <v>150.8179616228907</v>
       </c>
       <c r="E91">
-        <v>436.144</v>
+        <v>444.24</v>
       </c>
       <c r="F91">
-        <v>720.544</v>
+        <v>728.64</v>
       </c>
       <c r="G91">
         <v>162.1</v>
@@ -8877,37 +8877,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M91">
-        <v>169.9042752</v>
+        <v>171.813312</v>
       </c>
       <c r="N91">
-        <v>-116.7820529777778</v>
+        <v>-118.6910897777778</v>
       </c>
       <c r="O91">
-        <v>-11.67820529777778</v>
+        <v>-11.86910897777778</v>
       </c>
       <c r="P91">
-        <v>-105.10384768</v>
+        <v>-106.8219808</v>
       </c>
       <c r="Q91">
-        <v>-86.00384768000001</v>
+        <v>-87.72198080000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3612831246859872</v>
+        <v>0.392831437154586</v>
       </c>
       <c r="T91">
-        <v>6.323436479760789</v>
+        <v>6.955780127736868</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03126597147699213</v>
+        <v>0.03091857179391444</v>
       </c>
       <c r="W91">
-        <v>0.2284274839257253</v>
+        <v>0.228509400770995</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3126597147699213</v>
+        <v>0.3091857179391444</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2449416044093541</v>
+        <v>0.2468416044093541</v>
       </c>
       <c r="C92">
-        <v>-415.7220383771093</v>
+        <v>-425.1557037163662</v>
       </c>
       <c r="D92">
-        <v>150.8179616228907</v>
+        <v>149.4802962836337</v>
       </c>
       <c r="E92">
-        <v>444.24</v>
+        <v>452.336</v>
       </c>
       <c r="F92">
-        <v>728.64</v>
+        <v>736.736</v>
       </c>
       <c r="G92">
         <v>162.1</v>
@@ -8959,37 +8959,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M92">
-        <v>171.813312</v>
+        <v>173.7223488</v>
       </c>
       <c r="N92">
-        <v>-118.6910897777778</v>
+        <v>-120.6001265777778</v>
       </c>
       <c r="O92">
-        <v>-11.86910897777778</v>
+        <v>-12.06001265777778</v>
       </c>
       <c r="P92">
-        <v>-106.8219808</v>
+        <v>-108.54011392</v>
       </c>
       <c r="Q92">
-        <v>-87.72198080000001</v>
+        <v>-89.44011392000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.392831437154586</v>
+        <v>0.4313904857273178</v>
       </c>
       <c r="T92">
-        <v>6.955780127736868</v>
+        <v>7.728644586374299</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03091857179391444</v>
+        <v>0.03057880726870659</v>
       </c>
       <c r="W92">
-        <v>0.228509400770995</v>
+        <v>0.228589517246039</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3091857179391444</v>
+        <v>0.3057880726870659</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2468416044093541</v>
+        <v>0.2487416044093541</v>
       </c>
       <c r="C93">
-        <v>-425.1557037163662</v>
+        <v>-434.5658490768282</v>
       </c>
       <c r="D93">
-        <v>149.4802962836337</v>
+        <v>148.166150923172</v>
       </c>
       <c r="E93">
-        <v>452.336</v>
+        <v>460.4320000000001</v>
       </c>
       <c r="F93">
-        <v>736.736</v>
+        <v>744.8320000000001</v>
       </c>
       <c r="G93">
         <v>162.1</v>
@@ -9041,37 +9041,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M93">
-        <v>173.7223488</v>
+        <v>175.6313856</v>
       </c>
       <c r="N93">
-        <v>-120.6001265777778</v>
+        <v>-122.5091633777778</v>
       </c>
       <c r="O93">
-        <v>-12.06001265777778</v>
+        <v>-12.25091633777778</v>
       </c>
       <c r="P93">
-        <v>-108.54011392</v>
+        <v>-110.2582470400001</v>
       </c>
       <c r="Q93">
-        <v>-89.44011392000002</v>
+        <v>-91.15824704000005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4313904857273178</v>
+        <v>0.4795892964432327</v>
       </c>
       <c r="T93">
-        <v>7.728644586374299</v>
+        <v>8.694725159671091</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03057880726870659</v>
+        <v>0.03024642892882934</v>
       </c>
       <c r="W93">
-        <v>0.228589517246039</v>
+        <v>0.228667892058582</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3057880726870659</v>
+        <v>0.3024642892882933</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487416044093541</v>
+        <v>0.2506416044093541</v>
       </c>
       <c r="C94">
-        <v>-434.5658490768282</v>
+        <v>-443.9530893751461</v>
       </c>
       <c r="D94">
-        <v>148.166150923172</v>
+        <v>146.874910624854</v>
       </c>
       <c r="E94">
-        <v>460.4320000000001</v>
+        <v>468.5280000000001</v>
       </c>
       <c r="F94">
-        <v>744.8320000000001</v>
+        <v>752.9280000000001</v>
       </c>
       <c r="G94">
         <v>162.1</v>
@@ -9123,37 +9123,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M94">
-        <v>175.6313856</v>
+        <v>177.5404224</v>
       </c>
       <c r="N94">
-        <v>-122.5091633777778</v>
+        <v>-124.4182001777778</v>
       </c>
       <c r="O94">
-        <v>-12.25091633777778</v>
+        <v>-12.44182001777778</v>
       </c>
       <c r="P94">
-        <v>-110.2582470400001</v>
+        <v>-111.97638016</v>
       </c>
       <c r="Q94">
-        <v>-91.15824704000005</v>
+        <v>-92.87638016000005</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4795892964432327</v>
+        <v>0.541559195935123</v>
       </c>
       <c r="T94">
-        <v>8.694725159671091</v>
+        <v>9.936828753909817</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03024642892882934</v>
+        <v>0.02992119851023977</v>
       </c>
       <c r="W94">
-        <v>0.228667892058582</v>
+        <v>0.2287445813912855</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3024642892882933</v>
+        <v>0.2992119851023977</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2506416044093541</v>
+        <v>0.2525416044093541</v>
       </c>
       <c r="C95">
-        <v>-443.9530893751461</v>
+        <v>-453.3180182776289</v>
       </c>
       <c r="D95">
-        <v>146.874910624854</v>
+        <v>145.6059817223712</v>
       </c>
       <c r="E95">
-        <v>468.5280000000001</v>
+        <v>476.6240000000001</v>
       </c>
       <c r="F95">
-        <v>752.9280000000001</v>
+        <v>761.0240000000001</v>
       </c>
       <c r="G95">
         <v>162.1</v>
@@ -9205,37 +9205,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M95">
-        <v>177.5404224</v>
+        <v>179.4494592</v>
       </c>
       <c r="N95">
-        <v>-124.4182001777778</v>
+        <v>-126.3272369777778</v>
       </c>
       <c r="O95">
-        <v>-12.44182001777778</v>
+        <v>-12.63272369777778</v>
       </c>
       <c r="P95">
-        <v>-111.97638016</v>
+        <v>-113.6945132800001</v>
       </c>
       <c r="Q95">
-        <v>-92.87638016000005</v>
+        <v>-94.59451328000006</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.541559195935123</v>
+        <v>0.6241857285909769</v>
       </c>
       <c r="T95">
-        <v>9.936828753909817</v>
+        <v>11.59296687956146</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02992119851023977</v>
+        <v>0.02960288788779042</v>
       </c>
       <c r="W95">
-        <v>0.2287445813912855</v>
+        <v>0.228819639036059</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2992119851023977</v>
+        <v>0.2960288788779041</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525416044093541</v>
+        <v>0.254441604409354</v>
       </c>
       <c r="C96">
-        <v>-453.3180182776289</v>
+        <v>-462.6612091103453</v>
       </c>
       <c r="D96">
-        <v>145.6059817223712</v>
+        <v>144.3587908896548</v>
       </c>
       <c r="E96">
-        <v>476.6240000000001</v>
+        <v>484.7200000000001</v>
       </c>
       <c r="F96">
-        <v>761.0240000000001</v>
+        <v>769.1200000000001</v>
       </c>
       <c r="G96">
         <v>162.1</v>
@@ -9287,37 +9287,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M96">
-        <v>179.4494592</v>
+        <v>181.358496</v>
       </c>
       <c r="N96">
-        <v>-126.3272369777778</v>
+        <v>-128.2362737777778</v>
       </c>
       <c r="O96">
-        <v>-12.63272369777778</v>
+        <v>-12.82362737777778</v>
       </c>
       <c r="P96">
-        <v>-113.6945132800001</v>
+        <v>-115.4126464</v>
       </c>
       <c r="Q96">
-        <v>-94.59451328000006</v>
+        <v>-96.31264640000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6241857285909769</v>
+        <v>0.7398628743091727</v>
       </c>
       <c r="T96">
-        <v>11.59296687956146</v>
+        <v>13.91156025547375</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02960288788779042</v>
+        <v>0.02929127854160315</v>
       </c>
       <c r="W96">
-        <v>0.228819639036059</v>
+        <v>0.22889311651989</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2960288788779041</v>
+        <v>0.2929127854160315</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.254441604409354</v>
+        <v>0.2563416044093541</v>
       </c>
       <c r="C97">
-        <v>-462.6612091103453</v>
+        <v>-471.9832157228485</v>
       </c>
       <c r="D97">
-        <v>144.3587908896548</v>
+        <v>143.1327842771516</v>
       </c>
       <c r="E97">
-        <v>484.7200000000001</v>
+        <v>492.8160000000001</v>
       </c>
       <c r="F97">
-        <v>769.1200000000001</v>
+        <v>777.2160000000001</v>
       </c>
       <c r="G97">
         <v>162.1</v>
@@ -9369,37 +9369,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M97">
-        <v>181.358496</v>
+        <v>183.2675328</v>
       </c>
       <c r="N97">
-        <v>-128.2362737777778</v>
+        <v>-130.1453105777778</v>
       </c>
       <c r="O97">
-        <v>-12.82362737777778</v>
+        <v>-13.01453105777778</v>
       </c>
       <c r="P97">
-        <v>-115.4126464</v>
+        <v>-117.13077952</v>
       </c>
       <c r="Q97">
-        <v>-96.31264640000003</v>
+        <v>-98.03077952000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7398628743091727</v>
+        <v>0.9133785928864664</v>
       </c>
       <c r="T97">
-        <v>13.91156025547375</v>
+        <v>17.3894503193422</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02929127854160315</v>
+        <v>0.02898616105679479</v>
       </c>
       <c r="W97">
-        <v>0.22889311651989</v>
+        <v>0.2289650632228078</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2929127854160315</v>
+        <v>0.2898616105679478</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2563416044093541</v>
+        <v>0.2582416044093541</v>
       </c>
       <c r="C98">
-        <v>-471.9832157228484</v>
+        <v>-481.2845733082595</v>
       </c>
       <c r="D98">
-        <v>143.1327842771516</v>
+        <v>141.9274266917405</v>
       </c>
       <c r="E98">
-        <v>492.816</v>
+        <v>500.912</v>
       </c>
       <c r="F98">
-        <v>777.216</v>
+        <v>785.312</v>
       </c>
       <c r="G98">
         <v>162.1</v>
@@ -9451,37 +9451,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M98">
-        <v>183.2675328</v>
+        <v>185.1765696</v>
       </c>
       <c r="N98">
-        <v>-130.1453105777778</v>
+        <v>-132.0543473777778</v>
       </c>
       <c r="O98">
-        <v>-13.01453105777778</v>
+        <v>-13.20543473777778</v>
       </c>
       <c r="P98">
-        <v>-117.13077952</v>
+        <v>-118.84891264</v>
       </c>
       <c r="Q98">
-        <v>-98.03077952000001</v>
+        <v>-99.74891264000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9133785928864639</v>
+        <v>1.202571457181952</v>
       </c>
       <c r="T98">
-        <v>17.38945031934215</v>
+        <v>23.18593375912288</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02898616105679479</v>
+        <v>0.02868733465414742</v>
       </c>
       <c r="W98">
-        <v>0.2289650632228078</v>
+        <v>0.229035526488552</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2898616105679478</v>
+        <v>0.2868733465414741</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2582416044093541</v>
+        <v>0.2601416044093541</v>
       </c>
       <c r="C99">
-        <v>-481.2845733082595</v>
+        <v>-490.5657991822608</v>
       </c>
       <c r="D99">
-        <v>141.9274266917405</v>
+        <v>140.7422008177392</v>
       </c>
       <c r="E99">
-        <v>500.912</v>
+        <v>509.008</v>
       </c>
       <c r="F99">
-        <v>785.312</v>
+        <v>793.408</v>
       </c>
       <c r="G99">
         <v>162.1</v>
@@ -9533,37 +9533,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M99">
-        <v>185.1765696</v>
+        <v>187.0856064</v>
       </c>
       <c r="N99">
-        <v>-132.0543473777778</v>
+        <v>-133.9633841777778</v>
       </c>
       <c r="O99">
-        <v>-13.20543473777778</v>
+        <v>-13.39633841777778</v>
       </c>
       <c r="P99">
-        <v>-118.84891264</v>
+        <v>-120.56704576</v>
       </c>
       <c r="Q99">
-        <v>-99.74891264000004</v>
+        <v>-101.46704576</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.202571457181952</v>
+        <v>1.780957185772928</v>
       </c>
       <c r="T99">
-        <v>23.18593375912288</v>
+        <v>34.77890063868431</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02868733465414742</v>
+        <v>0.02839460674951326</v>
       </c>
       <c r="W99">
-        <v>0.229035526488552</v>
+        <v>0.2291045517284648</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2868733465414741</v>
+        <v>0.2839460674951325</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2601416044093541</v>
+        <v>0.2620416044093541</v>
       </c>
       <c r="C100">
-        <v>-490.5657991822608</v>
+        <v>-499.8273935233792</v>
       </c>
       <c r="D100">
-        <v>140.7422008177392</v>
+        <v>139.5766064766209</v>
       </c>
       <c r="E100">
-        <v>509.008</v>
+        <v>517.104</v>
       </c>
       <c r="F100">
-        <v>793.408</v>
+        <v>801.504</v>
       </c>
       <c r="G100">
         <v>162.1</v>
@@ -9615,37 +9615,37 @@
         <v>53.12222222222221</v>
       </c>
       <c r="M100">
-        <v>187.0856064</v>
+        <v>188.9946432</v>
       </c>
       <c r="N100">
-        <v>-133.9633841777778</v>
+        <v>-135.8724209777778</v>
       </c>
       <c r="O100">
-        <v>-13.39633841777778</v>
+        <v>-13.58724209777778</v>
       </c>
       <c r="P100">
-        <v>-120.56704576</v>
+        <v>-122.28517888</v>
       </c>
       <c r="Q100">
-        <v>-101.46704576</v>
+        <v>-103.18517888</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.780957185772928</v>
+        <v>3.516114371545856</v>
       </c>
       <c r="T100">
-        <v>34.77890063868431</v>
+        <v>69.55780127736861</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02839460674951326</v>
+        <v>0.02810779253992222</v>
       </c>
       <c r="W100">
-        <v>0.2291045517284648</v>
+        <v>0.2291721825190864</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2839460674951325</v>
+        <v>0.2810779253992222</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2620416044093541</v>
-      </c>
-      <c r="C101">
-        <v>-499.8273935233792</v>
-      </c>
-      <c r="D101">
-        <v>139.5766064766209</v>
-      </c>
-      <c r="E101">
-        <v>517.104</v>
-      </c>
-      <c r="F101">
-        <v>801.504</v>
-      </c>
-      <c r="G101">
-        <v>162.1</v>
-      </c>
-      <c r="H101">
-        <v>525.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>72.22222222222221</v>
-      </c>
-      <c r="K101">
-        <v>19.1</v>
-      </c>
-      <c r="L101">
-        <v>53.12222222222221</v>
-      </c>
-      <c r="M101">
-        <v>188.9946432</v>
-      </c>
-      <c r="N101">
-        <v>-135.8724209777778</v>
-      </c>
-      <c r="O101">
-        <v>-13.58724209777778</v>
-      </c>
-      <c r="P101">
-        <v>-122.28517888</v>
-      </c>
-      <c r="Q101">
-        <v>-103.18517888</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.516114371545856</v>
-      </c>
-      <c r="T101">
-        <v>69.55780127736861</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02810779253992222</v>
-      </c>
-      <c r="W101">
-        <v>0.2291721825190864</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2810779253992222</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
